--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Condition, Variation Problem</t>
+    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR Condition</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR Condition</t>
+    <t>This StructureDefinition contains the maps for VistA PROBLEM (file 9000011) to FHIR Condition</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -620,7 +620,7 @@
     <t>The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-clinical</t>
+    <t>http://va.gov/fhir/ValueSet/VFproblemStatus</t>
   </si>
   <si>
     <t>con-3
@@ -662,7 +662,7 @@
 The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-ver-status</t>
+    <t>http://va.gov/fhir/ValueSet/VFproblemVerificationStatus</t>
   </si>
   <si>
     <t>con-3
@@ -719,7 +719,7 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>1607: fixed value = http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item</t>
+    <t>1607: fixed value = http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item if PROBLEM (#9000011)</t>
   </si>
   <si>
     <t>Condition.category:us-core</t>
@@ -1808,7 +1808,7 @@
     <col min="41" max="41" width="16.3984375" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="11.54296875" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="42.1171875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="105.0703125" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="112.734375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -255,10 +255,10 @@
     <t>Mapping: SNOMED CT Attribute Binding</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -775,10 +775,10 @@
     <t>FiveWs.status</t>
   </si>
   <si>
+    <t>605: terminologyMaps using VF_problemStatus on PROBLEM - STATUS (#9000011-.12)</t>
+  </si>
+  <si>
     <t>Outpat.ProblemList.ActiveFlag</t>
-  </si>
-  <si>
-    <t>605: terminologyMaps using VF_problemStatus on PROBLEM - STATUS (#9000011-.12)</t>
   </si>
   <si>
     <t>Condition.verificationStatus</t>
@@ -814,10 +814,10 @@
     <t>408729009</t>
   </si>
   <si>
+    <t>611: terminologyMaps using VF_problemVerificationStatus on PROBLEM - CONDITION (#9000011-1.02)</t>
+  </si>
+  <si>
     <t>Outpat.ProblemList.ProblemListCondition</t>
-  </si>
-  <si>
-    <t>611: terminologyMaps using VF_problemVerificationStatus on PROBLEM - CONDITION (#9000011-1.02)</t>
   </si>
   <si>
     <t>Condition.category</t>
@@ -837,6 +837,10 @@
   <si>
     <t xml:space="preserve">pattern:$this}
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-0:1607: fixed value "http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item" {null}</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -962,10 +966,10 @@
     <t>246090004</t>
   </si>
   <si>
+    <t>958: source value from PROBLEM - MAPPING TARGETS &gt; MAPPING TARGETS (#9000011-80300 &gt; 9000011.803-)</t>
+  </si>
+  <si>
     <t>Outpat.ProblemList.ICDIEN</t>
-  </si>
-  <si>
-    <t>958: source value from PROBLEM - MAPPING TARGETS &gt; MAPPING TARGETS (#9000011-80300 &gt; 9000011.803-)</t>
   </si>
   <si>
     <t>Condition.code.id</t>
@@ -1074,10 +1078,10 @@
     <t>./code</t>
   </si>
   <si>
+    <t>366: source value from PROBLEM - SNOMED CT CONCEPT CODE (#9000011-80001)</t>
+  </si>
+  <si>
     <t>Outpat.ProblemList.SNOMEDCTConceptCode</t>
-  </si>
-  <si>
-    <t>366: source value from PROBLEM - SNOMED CT CONCEPT CODE (#9000011-80001)</t>
   </si>
   <si>
     <t>Condition.code.coding.display</t>
@@ -1153,10 +1157,10 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
+    <t>957: source value from PROBLEM - PROVIDER NARRATIVE (#9000011-.05)</t>
+  </si>
+  <si>
     <t>Outpat.ProblemList.ProviderNarrativeIEN</t>
-  </si>
-  <si>
-    <t>957: source value from PROBLEM - PROVIDER NARRATIVE (#9000011-.05)</t>
   </si>
   <si>
     <t>Condition.bodySite</t>
@@ -1221,10 +1225,10 @@
     <t>FiveWs.subject</t>
   </si>
   <si>
+    <t>367: reference from PROBLEM - PATIENT NAME (#9000011-.02)</t>
+  </si>
+  <si>
     <t>Outpat.ProblemList.PatientIEN</t>
-  </si>
-  <si>
-    <t>367: reference from PROBLEM - PATIENT NAME (#9000011-.02)</t>
   </si>
   <si>
     <t>Condition.encounter</t>
@@ -1297,10 +1301,10 @@
 </t>
   </si>
   <si>
+    <t>369: source value from PROBLEM - DATE OF ONSET (#9000011-.13)</t>
+  </si>
+  <si>
     <t>Outpat.ProblemList.OnsetDateTime</t>
-  </si>
-  <si>
-    <t>369: source value from PROBLEM - DATE OF ONSET (#9000011-.13)</t>
   </si>
   <si>
     <t>Condition.abatement[x]</t>
@@ -1343,10 +1347,10 @@
     <t>FiveWs.recorded</t>
   </si>
   <si>
+    <t>371: source value from PROBLEM - DATE ENTERED (#9000011-.08)</t>
+  </si>
+  <si>
     <t>Outpat.ProblemList.EnteredDateTime</t>
-  </si>
-  <si>
-    <t>371: source value from PROBLEM - DATE ENTERED (#9000011-.08)</t>
   </si>
   <si>
     <t>Condition.recorder</t>
@@ -1368,10 +1372,10 @@
     <t>FiveWs.author</t>
   </si>
   <si>
+    <t>373: source value from PROBLEM - RECORDING PROVIDER (#9000011-1.04)</t>
+  </si>
+  <si>
     <t>Outpat.ProblemList.RecordingProviderIEN</t>
-  </si>
-  <si>
-    <t>373: source value from PROBLEM - RECORDING PROVIDER (#9000011-1.04)</t>
   </si>
   <si>
     <t>Condition.asserter</t>
@@ -1940,8 +1944,8 @@
     <col min="40" max="40" width="222.1015625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="112.734375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="112.734375" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4218,10 +4222,10 @@
         <v>81</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>81</v>
+        <v>217</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>217</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -4819,42 +4823,42 @@
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>264</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>268</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>258</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>81</v>
@@ -4879,7 +4883,7 @@
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>260</v>
@@ -4915,7 +4919,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4951,16 +4955,16 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -4974,13 +4978,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>258</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>81</v>
@@ -5005,7 +5009,7 @@
         <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>260</v>
@@ -5022,7 +5026,7 @@
         <v>81</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>81</v>
@@ -5079,16 +5083,16 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5102,10 +5106,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5131,13 +5135,13 @@
         <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5166,10 +5170,10 @@
         <v>117</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5187,7 +5191,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5205,19 +5209,19 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>81</v>
@@ -5228,14 +5232,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5257,14 +5261,14 @@
         <v>190</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5292,10 +5296,10 @@
         <v>195</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5313,7 +5317,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5328,36 +5332,36 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5478,10 +5482,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5604,10 +5608,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5630,19 +5634,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5691,7 +5695,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5712,10 +5716,10 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5732,10 +5736,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5856,10 +5860,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5982,10 +5986,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6011,16 +6015,16 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -6069,7 +6073,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6090,10 +6094,10 @@
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -6110,10 +6114,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6139,13 +6143,13 @@
         <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6195,7 +6199,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6216,10 +6220,10 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6236,10 +6240,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6265,14 +6269,14 @@
         <v>113</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6321,7 +6325,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6342,10 +6346,10 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6354,18 +6358,18 @@
         <v>81</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6391,14 +6395,14 @@
         <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6447,7 +6451,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6468,10 +6472,10 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6488,10 +6492,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6514,19 +6518,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6575,7 +6579,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6596,10 +6600,10 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6616,10 +6620,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6645,16 +6649,16 @@
         <v>169</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6703,7 +6707,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6724,10 +6728,10 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6736,18 +6740,18 @@
         <v>81</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6773,13 +6777,13 @@
         <v>190</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6805,13 +6809,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6829,7 +6833,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6847,19 +6851,19 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>81</v>
@@ -6870,14 +6874,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6896,17 +6900,17 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6955,7 +6959,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>93</v>
@@ -6970,36 +6974,36 @@
         <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7022,16 +7026,16 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7081,7 +7085,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7096,19 +7100,19 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
@@ -7122,10 +7126,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7148,16 +7152,16 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7195,7 +7199,7 @@
         <v>81</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7205,7 +7209,7 @@
         <v>142</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7220,19 +7224,19 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>81</v>
@@ -7246,13 +7250,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>81</v>
@@ -7274,16 +7278,16 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7333,7 +7337,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7348,36 +7352,36 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7400,16 +7404,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7459,7 +7463,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7468,7 +7472,7 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>105</v>
@@ -7483,10 +7487,10 @@
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -7500,10 +7504,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7526,13 +7530,13 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7583,7 +7587,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7604,30 +7608,30 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7650,13 +7654,13 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7707,7 +7711,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7731,27 +7735,27 @@
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7774,13 +7778,13 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7831,7 +7835,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7852,13 +7856,13 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -7872,10 +7876,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7898,13 +7902,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7955,7 +7959,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7967,7 +7971,7 @@
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7979,7 +7983,7 @@
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -7996,10 +8000,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8120,10 +8124,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8246,14 +8250,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8275,10 +8279,10 @@
         <v>138</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>156</v>
@@ -8333,7 +8337,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8374,10 +8378,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8403,10 +8407,10 @@
         <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8433,13 +8437,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8457,7 +8461,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8466,7 +8470,7 @@
         <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>105</v>
@@ -8475,13 +8479,13 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>241</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
@@ -8498,10 +8502,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8524,13 +8528,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8581,7 +8585,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8590,7 +8594,7 @@
         <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8605,7 +8609,7 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8622,10 +8626,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8651,10 +8655,10 @@
         <v>190</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8681,13 +8685,13 @@
         <v>81</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8705,7 +8709,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8729,7 +8733,7 @@
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8746,10 +8750,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8772,16 +8776,16 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8831,7 +8835,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8843,7 +8847,7 @@
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
@@ -8855,7 +8859,7 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8872,10 +8876,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8996,10 +9000,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9122,14 +9126,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9151,10 +9155,10 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>156</v>
@@ -9209,7 +9213,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9250,10 +9254,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9279,10 +9283,10 @@
         <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9309,13 +9313,13 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -9333,7 +9337,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9342,25 +9346,25 @@
         <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
@@ -9374,10 +9378,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9400,13 +9404,13 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9457,7 +9461,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9466,7 +9470,7 @@
         <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9481,10 +9485,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -9498,10 +9502,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9524,13 +9528,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9581,7 +9585,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9596,16 +9600,16 @@
         <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -840,7 +840,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-0:1607: fixed value "http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item" {null}</t>
+inv-0:1607: fixed value = http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item if PROBLEM (#9000011) {null}</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA PROBLEM (file 9000011) to FHIR Condition</t>
+    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR Condition</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -840,7 +840,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-0:1607: fixed value = http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item if PROBLEM (#9000011) {null}</t>
+inv-0:1607: fixed value = http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item {null}</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -855,7 +855,7 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>1607: fixed value = http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item if PROBLEM (#9000011)</t>
+    <t>1607: fixed value = http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item</t>
   </si>
   <si>
     <t>Condition.category:us-core</t>
@@ -1944,7 +1944,7 @@
     <col min="40" max="40" width="222.1015625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="112.734375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="105.0703125" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -832,6 +832,14 @@
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/condition-category"/&gt;
+    &lt;code value="problem-list-item"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/condition-category</t>
   </si>
   <si>
@@ -851,7 +859,7 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>1607: fixed value = http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item when PROBLEM - . (#9000011-)</t>
+    <t>1607: fixed value = http://terminology.hl7.org/CodeSystem/condition-category#problem-list-item when PROBLEM - . (#9000011-)</t>
   </si>
   <si>
     <t>Condition.category:us-core</t>
@@ -1940,7 +1948,7 @@
     <col min="40" max="40" width="222.1015625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="119.6015625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="120.5234375" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -4770,7 +4778,7 @@
         <v>81</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>81</v>
@@ -4791,13 +4799,13 @@
         <v>260</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4825,22 +4833,22 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>81</v>
@@ -4848,13 +4856,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>258</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>81</v>
@@ -4879,7 +4887,7 @@
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>260</v>
@@ -4915,7 +4923,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4951,16 +4959,16 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -4974,13 +4982,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>258</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>81</v>
@@ -5005,7 +5013,7 @@
         <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>260</v>
@@ -5022,7 +5030,7 @@
         <v>81</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>81</v>
@@ -5043,7 +5051,7 @@
         <v>260</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -5079,16 +5087,16 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5102,10 +5110,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5131,13 +5139,13 @@
         <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5166,10 +5174,10 @@
         <v>117</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5187,7 +5195,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5205,19 +5213,19 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>81</v>
@@ -5228,14 +5236,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5257,14 +5265,14 @@
         <v>190</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5292,10 +5300,10 @@
         <v>195</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5313,7 +5321,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5328,36 +5336,36 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5478,10 +5486,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5604,10 +5612,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5630,19 +5638,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5691,7 +5699,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5712,10 +5720,10 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5732,10 +5740,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5856,10 +5864,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5982,10 +5990,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6011,16 +6019,16 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -6069,7 +6077,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6090,10 +6098,10 @@
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -6110,10 +6118,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6139,13 +6147,13 @@
         <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6195,7 +6203,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6216,10 +6224,10 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6236,10 +6244,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6265,14 +6273,14 @@
         <v>113</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6321,7 +6329,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6342,10 +6350,10 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6354,18 +6362,18 @@
         <v>81</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6391,14 +6399,14 @@
         <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6447,7 +6455,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6468,10 +6476,10 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6488,10 +6496,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6514,19 +6522,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6575,7 +6583,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6596,10 +6604,10 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6616,10 +6624,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6645,16 +6653,16 @@
         <v>169</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6703,7 +6711,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6724,10 +6732,10 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6736,18 +6744,18 @@
         <v>81</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6773,13 +6781,13 @@
         <v>190</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6805,13 +6813,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6829,7 +6837,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6847,19 +6855,19 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>81</v>
@@ -6870,14 +6878,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6896,17 +6904,17 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6955,7 +6963,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>93</v>
@@ -6970,36 +6978,36 @@
         <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7022,16 +7030,16 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7081,7 +7089,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7096,19 +7104,19 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
@@ -7122,10 +7130,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7148,16 +7156,16 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7195,7 +7203,7 @@
         <v>81</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7205,7 +7213,7 @@
         <v>142</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7220,19 +7228,19 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>81</v>
@@ -7246,13 +7254,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>81</v>
@@ -7274,16 +7282,16 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7333,7 +7341,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7348,36 +7356,36 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7400,16 +7408,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7459,7 +7467,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7468,7 +7476,7 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>105</v>
@@ -7483,10 +7491,10 @@
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -7500,10 +7508,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7526,13 +7534,13 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7583,7 +7591,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7604,30 +7612,30 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7650,13 +7658,13 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7707,7 +7715,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7731,27 +7739,27 @@
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7774,13 +7782,13 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7831,7 +7839,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7852,13 +7860,13 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>81</v>
@@ -7872,10 +7880,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7898,13 +7906,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7955,7 +7963,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7967,7 +7975,7 @@
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7979,7 +7987,7 @@
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -7996,10 +8004,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8120,10 +8128,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8246,14 +8254,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8275,10 +8283,10 @@
         <v>138</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>156</v>
@@ -8333,7 +8341,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8374,10 +8382,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8403,10 +8411,10 @@
         <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8433,13 +8441,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8457,7 +8465,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8466,7 +8474,7 @@
         <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>105</v>
@@ -8475,13 +8483,13 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>241</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
@@ -8498,10 +8506,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8524,13 +8532,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8581,7 +8589,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8590,7 +8598,7 @@
         <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8605,7 +8613,7 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8622,10 +8630,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8651,10 +8659,10 @@
         <v>190</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8681,13 +8689,13 @@
         <v>81</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8705,7 +8713,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8729,7 +8737,7 @@
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8746,10 +8754,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8772,16 +8780,16 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8831,7 +8839,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8843,7 +8851,7 @@
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
@@ -8855,7 +8863,7 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8872,10 +8880,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8996,10 +9004,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9122,14 +9130,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9151,10 +9159,10 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>156</v>
@@ -9209,7 +9217,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9250,10 +9258,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9279,10 +9287,10 @@
         <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9309,13 +9317,13 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -9333,7 +9341,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9342,25 +9350,25 @@
         <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>81</v>
@@ -9374,10 +9382,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9400,13 +9408,13 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9457,7 +9465,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9466,7 +9474,7 @@
         <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9481,10 +9489,10 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>81</v>
@@ -9498,10 +9506,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9524,13 +9532,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9581,7 +9589,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9596,16 +9604,16 @@
         <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -684,13 +684,13 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>345: source value from PROBLEM - IEN (#9000011-.001)</t>
+  </si>
+  <si>
     <t>CX.1 / EI.1</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>345: source value from PROBLEM - IEN (#9000011-.001)</t>
   </si>
   <si>
     <t>Condition.identifier.period</t>
@@ -759,6 +759,12 @@
 con-4con-5</t>
   </si>
   <si>
+    <t>605: terminologyMaps using VF_problemStatus on PROBLEM - STATUS (#9000011-.12)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.ActiveFlag</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -775,12 +781,6 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>605: terminologyMaps using VF_problemStatus on PROBLEM - STATUS (#9000011-.12)</t>
-  </si>
-  <si>
-    <t>Outpat.ProblemList.ActiveFlag</t>
-  </si>
-  <si>
     <t>Condition.verificationStatus</t>
   </si>
   <si>
@@ -801,6 +801,12 @@
 con-5</t>
   </si>
   <si>
+    <t>611: terminologyMaps using VF_problemVerificationStatus on PROBLEM - CONDITION (#9000011-1.02)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.ProblemListCondition</t>
+  </si>
+  <si>
     <t>&lt; 410514004 |Finding context value|</t>
   </si>
   <si>
@@ -814,12 +820,6 @@
     <t>408729009</t>
   </si>
   <si>
-    <t>611: terminologyMaps using VF_problemVerificationStatus on PROBLEM - CONDITION (#9000011-1.02)</t>
-  </si>
-  <si>
-    <t>Outpat.ProblemList.ProblemListCondition</t>
-  </si>
-  <si>
     <t>Condition.category</t>
   </si>
   <si>
@@ -830,6 +830,34 @@
   </si>
   <si>
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>&lt; 404684003 |Clinical finding|</t>
+  </si>
+  <si>
+    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Condition.category:us-core</t>
+  </si>
+  <si>
+    <t>us-core</t>
+  </si>
+  <si>
+    <t>problem-list-item | health-concern</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -840,38 +868,10 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>&lt; 404684003 |Clinical finding|</t>
-  </si>
-  <si>
-    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>1607: fixed value = http://terminology.hl7.org/CodeSystem/condition-category#problem-list-item when PROBLEM - . (#9000011-)</t>
-  </si>
-  <si>
-    <t>Condition.category:us-core</t>
-  </si>
-  <si>
-    <t>us-core</t>
-  </si>
-  <si>
-    <t>problem-list-item | health-concern</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-problem-or-health-concern</t>
+  </si>
+  <si>
+    <t>1607: fixed value = http://terminology.hl7.org/CodeSystem/condition-category#problem-list-item</t>
   </si>
   <si>
     <t>Condition.category:sdoh</t>
@@ -941,6 +941,12 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
+  </si>
+  <si>
+    <t>365: source value from PROBLEM - DIAGNOSIS &gt; ICD DIAGNOSIS (#9000011-.01 &gt; 80-)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.ICDIEN</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -970,12 +976,6 @@
     <t>246090004</t>
   </si>
   <si>
-    <t>958: source value from PROBLEM - MAPPING TARGETS &gt; MAPPING TARGETS (#9000011-80300 &gt; 9000011.803-)</t>
-  </si>
-  <si>
-    <t>Outpat.ProblemList.ICDIEN</t>
-  </si>
-  <si>
     <t>Condition.code.id</t>
   </si>
   <si>
@@ -1076,16 +1076,16 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>366: source value from PROBLEM - SNOMED CT CONCEPT CODE (#9000011-80001)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.SNOMEDCTConceptCode</t>
+  </si>
+  <si>
     <t>C*E.1</t>
   </si>
   <si>
     <t>./code</t>
-  </si>
-  <si>
-    <t>366: source value from PROBLEM - SNOMED CT CONCEPT CODE (#9000011-80001)</t>
-  </si>
-  <si>
-    <t>Outpat.ProblemList.SNOMEDCTConceptCode</t>
   </si>
   <si>
     <t>Condition.code.coding.display</t>
@@ -1155,16 +1155,16 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>957: source value from PROBLEM - PROVIDER NARRATIVE (#9000011-.05)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.ProviderNarrativeIEN</t>
+  </si>
+  <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>957: source value from PROBLEM - PROVIDER NARRATIVE (#9000011-.05)</t>
-  </si>
-  <si>
-    <t>Outpat.ProblemList.ProviderNarrativeIEN</t>
   </si>
   <si>
     <t>Condition.bodySite</t>
@@ -1217,6 +1217,12 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
+    <t>367: reference from PROBLEM - PATIENT NAME (#9000011-.02)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1227,12 +1233,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>367: reference from PROBLEM - PATIENT NAME (#9000011-.02)</t>
-  </si>
-  <si>
-    <t>Outpat.ProblemList.PatientIEN</t>
   </si>
   <si>
     <t>Condition.encounter</t>
@@ -1342,6 +1342,12 @@
     <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
   </si>
   <si>
+    <t>371: source value from PROBLEM - DATE ENTERED (#9000011-.08)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.EnteredDateTime</t>
+  </si>
+  <si>
     <t>REL-11</t>
   </si>
   <si>
@@ -1349,12 +1355,6 @@
   </si>
   <si>
     <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>371: source value from PROBLEM - DATE ENTERED (#9000011-.08)</t>
-  </si>
-  <si>
-    <t>Outpat.ProblemList.EnteredDateTime</t>
   </si>
   <si>
     <t>Condition.recorder</t>
@@ -1370,16 +1370,16 @@
     <t>Individual who recorded the record and takes responsibility for its content.</t>
   </si>
   <si>
+    <t>373: source value from PROBLEM - RECORDING PROVIDER (#9000011-1.04)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.RecordingProviderIEN</t>
+  </si>
+  <si>
     <t>.participation[typeCode=AUT].role</t>
   </si>
   <si>
     <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>373: source value from PROBLEM - RECORDING PROVIDER (#9000011-1.04)</t>
-  </si>
-  <si>
-    <t>Outpat.ProblemList.RecordingProviderIEN</t>
   </si>
   <si>
     <t>Condition.asserter</t>
@@ -1942,14 +1942,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="68.20703125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="222.1015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="120.5234375" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="95.98046875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="68.20703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="222.1015625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2188,22 +2188,22 @@
         <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>81</v>
@@ -2825,13 +2825,13 @@
         <v>81</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>81</v>
@@ -2951,13 +2951,13 @@
         <v>81</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>81</v>
@@ -3329,13 +3329,13 @@
         <v>81</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP11" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ11" t="s" s="2">
         <v>81</v>
@@ -3448,25 +3448,25 @@
         <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AN12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AO12" t="s" s="2">
+      <c r="AQ12" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ12" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR12" t="s" s="2">
         <v>81</v>
@@ -3581,13 +3581,13 @@
         <v>81</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>81</v>
@@ -3707,13 +3707,13 @@
         <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>81</v>
@@ -3832,16 +3832,16 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>81</v>
@@ -3960,16 +3960,16 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>81</v>
@@ -4088,16 +4088,16 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>81</v>
@@ -4208,25 +4208,25 @@
         <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO18" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AP18" t="s" s="2">
-        <v>81</v>
+        <v>217</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>81</v>
@@ -4338,16 +4338,16 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>81</v>
@@ -4464,16 +4464,16 @@
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>81</v>
@@ -4597,13 +4597,13 @@
         <v>243</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4706,25 +4706,25 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>254</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>257</v>
@@ -4778,7 +4778,7 @@
         <v>81</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>81</v>
@@ -4799,13 +4799,13 @@
         <v>260</v>
       </c>
       <c r="Z23" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4833,22 +4833,22 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>81</v>
@@ -4856,13 +4856,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>258</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>81</v>
@@ -4887,7 +4887,7 @@
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>260</v>
@@ -4904,7 +4904,7 @@
         <v>81</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>81</v>
+        <v>271</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>81</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4956,25 +4956,25 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>81</v>
@@ -5051,7 +5051,7 @@
         <v>260</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -5087,22 +5087,22 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>81</v>
@@ -5213,25 +5213,25 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AR26" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5469,13 +5469,13 @@
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>81</v>
@@ -5595,13 +5595,13 @@
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>81</v>
@@ -5720,16 +5720,16 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>81</v>
@@ -5847,13 +5847,13 @@
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -5973,13 +5973,13 @@
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>81</v>
@@ -6098,16 +6098,16 @@
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>81</v>
@@ -6224,16 +6224,16 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>81</v>
@@ -6344,28 +6344,28 @@
         <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>81</v>
+        <v>337</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>337</v>
+        <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>338</v>
+        <v>81</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>339</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6476,16 +6476,16 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>81</v>
@@ -6604,16 +6604,16 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6726,28 +6726,28 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>81</v>
+        <v>362</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>362</v>
+        <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>363</v>
+        <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>81</v>
+        <v>364</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>364</v>
+        <v>81</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>365</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -6855,25 +6855,25 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AO39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR39" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="40" hidden="true">
@@ -6981,25 +6981,25 @@
         <v>382</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>384</v>
+        <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>385</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>387</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -7104,25 +7104,25 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>81</v>
@@ -7228,25 +7228,25 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AL42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AO42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>81</v>
@@ -7356,28 +7356,28 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AP43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>410</v>
-      </c>
       <c r="AR43" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7491,16 +7491,16 @@
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>81</v>
@@ -7606,28 +7606,28 @@
         <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>424</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>426</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -7730,28 +7730,28 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>432</v>
+        <v>81</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>81</v>
+        <v>433</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>434</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7860,19 +7860,19 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>81</v>
@@ -7987,13 +7987,13 @@
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>81</v>
@@ -8111,13 +8111,13 @@
         <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
@@ -8237,13 +8237,13 @@
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>81</v>
@@ -8365,13 +8365,13 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -8483,19 +8483,19 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="AO52" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>81</v>
@@ -8613,13 +8613,13 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>81</v>
@@ -8737,13 +8737,13 @@
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>81</v>
@@ -8863,13 +8863,13 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>81</v>
@@ -8987,13 +8987,13 @@
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>81</v>
@@ -9113,13 +9113,13 @@
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>81</v>
@@ -9241,13 +9241,13 @@
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
@@ -9356,25 +9356,25 @@
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AN59" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AO59" t="s" s="2">
+      <c r="AQ59" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -9489,16 +9489,16 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AO60" t="s" s="2">
+      <c r="AQ60" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>81</v>
@@ -9604,22 +9604,22 @@
         <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AL61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AP61" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$62</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2512" uniqueCount="505">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1331,6 +1331,18 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementDateTime</t>
+  </si>
+  <si>
+    <t>abatementDateTime</t>
+  </si>
+  <si>
+    <t>1761: source value from PROBLEM - DATE RESOLVED (#9000011-1.07)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.ResolvedDateTime</t>
   </si>
   <si>
     <t>Condition.recordedDate</t>
@@ -1904,12 +1916,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR61"/>
+  <dimension ref="A1:AR62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.5390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.88671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.0546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="20.01953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -7455,16 +7467,14 @@
         <v>81</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>412</v>
@@ -7511,9 +7521,11 @@
         <v>419</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7531,18 +7543,20 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>409</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7591,7 +7605,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7600,17 +7614,17 @@
         <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AL45" t="s" s="2">
-        <v>423</v>
-      </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7618,13 +7632,13 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>81</v>
@@ -7632,10 +7646,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7658,13 +7672,13 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7715,7 +7729,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7730,10 +7744,10 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7742,13 +7756,13 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>81</v>
+        <v>428</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>81</v>
@@ -7756,10 +7770,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7773,7 +7787,7 @@
         <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>81</v>
@@ -7782,13 +7796,13 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7839,7 +7853,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7854,10 +7868,10 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7866,13 +7880,13 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>81</v>
@@ -7880,10 +7894,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7894,7 +7908,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7903,16 +7917,16 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7963,19 +7977,19 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>445</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7990,13 +8004,13 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>81</v>
@@ -8004,10 +8018,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8018,7 +8032,7 @@
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -8030,13 +8044,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>169</v>
+        <v>446</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>170</v>
+        <v>447</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>171</v>
+        <v>448</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8087,19 +8101,19 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>172</v>
+        <v>445</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -8117,7 +8131,7 @@
         <v>81</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>173</v>
+        <v>450</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
@@ -8128,21 +8142,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -8154,17 +8168,15 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8213,19 +8225,19 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
@@ -8254,14 +8266,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>450</v>
+        <v>153</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8274,26 +8286,24 @@
         <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>451</v>
+        <v>175</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>452</v>
+        <v>176</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="O51" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8341,7 +8351,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>453</v>
+        <v>178</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8371,7 +8381,7 @@
         <v>81</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>81</v>
@@ -8382,33 +8392,33 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>81</v>
+        <v>454</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>455</v>
@@ -8416,8 +8426,12 @@
       <c r="M52" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="N52" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8441,43 +8455,43 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>459</v>
+        <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>81</v>
@@ -8489,13 +8503,13 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>460</v>
+        <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>300</v>
+        <v>136</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>81</v>
@@ -8506,10 +8520,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8520,7 +8534,7 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -8532,13 +8546,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>462</v>
+        <v>190</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8565,13 +8579,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>81</v>
+        <v>370</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>81</v>
+        <v>462</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8589,16 +8603,16 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8613,13 +8627,13 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>81</v>
+        <v>464</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>465</v>
+        <v>300</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>81</v>
@@ -8630,10 +8644,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8644,7 +8658,7 @@
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8656,7 +8670,7 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>190</v>
+        <v>466</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>467</v>
@@ -8689,13 +8703,13 @@
         <v>81</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>469</v>
+        <v>81</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>470</v>
+        <v>81</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8713,16 +8727,16 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>105</v>
@@ -8743,7 +8757,7 @@
         <v>81</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>81</v>
@@ -8754,10 +8768,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8768,7 +8782,7 @@
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8780,17 +8794,15 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>442</v>
+        <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8815,13 +8827,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>81</v>
+        <v>370</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>81</v>
+        <v>474</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8839,19 +8851,19 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>476</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
@@ -8869,7 +8881,7 @@
         <v>81</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>81</v>
@@ -8880,10 +8892,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8894,7 +8906,7 @@
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8906,15 +8918,17 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>169</v>
+        <v>446</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>170</v>
+        <v>477</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8963,19 +8977,19 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>172</v>
+        <v>476</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>81</v>
@@ -8993,7 +9007,7 @@
         <v>81</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>173</v>
+        <v>481</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>81</v>
@@ -9004,21 +9018,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -9030,17 +9044,15 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -9089,19 +9101,19 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
@@ -9130,14 +9142,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>450</v>
+        <v>153</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9150,26 +9162,24 @@
         <v>81</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>451</v>
+        <v>175</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>452</v>
+        <v>176</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
       </c>
@@ -9217,7 +9227,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>453</v>
+        <v>178</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9247,7 +9257,7 @@
         <v>81</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
@@ -9258,14 +9268,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>81</v>
+        <v>454</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9278,22 +9288,26 @@
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9317,13 +9331,13 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>484</v>
+        <v>81</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>485</v>
+        <v>81</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -9341,7 +9355,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9350,10 +9364,10 @@
         <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9362,19 +9376,19 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>487</v>
+        <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>488</v>
+        <v>136</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>489</v>
+        <v>81</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>81</v>
@@ -9382,10 +9396,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9408,13 +9422,13 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>491</v>
+        <v>190</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9441,13 +9455,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>81</v>
+        <v>370</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>81</v>
+        <v>489</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9465,7 +9479,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9474,7 +9488,7 @@
         <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9486,19 +9500,19 @@
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>81</v>
+        <v>491</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>81</v>
@@ -9529,7 +9543,7 @@
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>495</v>
@@ -9598,7 +9612,7 @@
         <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>81</v>
+        <v>490</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9610,26 +9624,150 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AR61" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AN61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO61" t="s" s="2">
+      <c r="B62" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K62" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AP61" t="s" s="2">
+      <c r="L62" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AQ61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR61" t="s" s="2">
+      <c r="M62" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR62" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR61">
+  <autoFilter ref="A1:AR62">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9639,7 +9777,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI61">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PROBLEM (#9000011) to us-core-condition-problems-health-concerns</t>
+    <t>This StructureDefinition contains the maps for VistA file PROBLEM (9000011) to us-core-condition-problems-health-concerns</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -684,7 +684,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>345: source value from PROBLEM - IEN (#9000011-.001)</t>
+    <t>345: source value from PROBLEM - IEN (9000011-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -759,7 +759,7 @@
 con-4con-5</t>
   </si>
   <si>
-    <t>605: terminologyMaps using VF_problemStatus on PROBLEM - STATUS (#9000011-.12)</t>
+    <t>605: terminologyMaps using VF_problemStatus on PROBLEM - STATUS (9000011-.12)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.ActiveFlag</t>
@@ -801,7 +801,7 @@
 con-5</t>
   </si>
   <si>
-    <t>611: terminologyMaps using VF_problemVerificationStatus on PROBLEM - CONDITION (#9000011-1.02)</t>
+    <t>611: terminologyMaps using VF_problemVerificationStatus on PROBLEM - CONDITION (9000011-1.02)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.ProblemListCondition</t>
@@ -943,7 +943,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
   </si>
   <si>
-    <t>365: source value from PROBLEM - DIAGNOSIS &gt; ICD DIAGNOSIS (#9000011-.01 &gt; 80-)</t>
+    <t>365: source value from PROBLEM - DIAGNOSIS &gt; ICD DIAGNOSIS (9000011-.01 &gt; 80-)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.ICDIEN</t>
@@ -1076,7 +1076,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>366: source value from PROBLEM - SNOMED CT CONCEPT CODE (#9000011-80001)</t>
+    <t>366: source value from PROBLEM - SNOMED CT CONCEPT CODE (9000011-80001)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.SNOMEDCTConceptCode</t>
@@ -1155,7 +1155,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>957: source value from PROBLEM - PROVIDER NARRATIVE (#9000011-.05)</t>
+    <t>957: source value from PROBLEM - PROVIDER NARRATIVE (9000011-.05)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.ProviderNarrativeIEN</t>
@@ -1217,7 +1217,7 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
-    <t>367: reference from PROBLEM - PATIENT NAME (#9000011-.02)</t>
+    <t>367: reference from PROBLEM - PATIENT NAME (9000011-.02)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.PatientIEN</t>
@@ -1305,7 +1305,7 @@
 </t>
   </si>
   <si>
-    <t>369: source value from PROBLEM - DATE OF ONSET (#9000011-.13)</t>
+    <t>369: source value from PROBLEM - DATE OF ONSET (9000011-.13)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.OnsetDateTime</t>
@@ -1339,7 +1339,7 @@
     <t>abatementDateTime</t>
   </si>
   <si>
-    <t>1761: source value from PROBLEM - DATE RESOLVED (#9000011-1.07)</t>
+    <t>1761: source value from PROBLEM - DATE RESOLVED (9000011-1.07)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.ResolvedDateTime</t>
@@ -1354,7 +1354,7 @@
     <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
   </si>
   <si>
-    <t>371: source value from PROBLEM - DATE ENTERED (#9000011-.08)</t>
+    <t>371: source value from PROBLEM - DATE ENTERED (9000011-.08)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.EnteredDateTime</t>
@@ -1382,7 +1382,7 @@
     <t>Individual who recorded the record and takes responsibility for its content.</t>
   </si>
   <si>
-    <t>373: source value from PROBLEM - RECORDING PROVIDER (#9000011-1.04)</t>
+    <t>373: source value from PROBLEM - RECORDING PROVIDER (9000011-1.04)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.RecordingProviderIEN</t>
@@ -1954,7 +1954,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="95.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="94.44140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2512" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2512" uniqueCount="509">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -654,10 +654,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>345-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -1031,7 +1037,13 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>Coding.system</t>
+  </si>
+  <si>
+    <t>366-1: fixed value = http://snomed.info/sct</t>
   </si>
   <si>
     <t>C*E.3</t>
@@ -4009,7 +4021,7 @@
         <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>81</v>
@@ -4040,10 +4052,10 @@
         <v>81</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>81</v>
@@ -4079,7 +4091,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4094,7 +4106,7 @@
         <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>81</v>
+        <v>208</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>81</v>
@@ -4106,10 +4118,10 @@
         <v>81</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>81</v>
@@ -4120,10 +4132,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4149,13 +4161,13 @@
         <v>169</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4169,7 +4181,7 @@
         <v>81</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>81</v>
@@ -4205,7 +4217,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4220,7 +4232,7 @@
         <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>81</v>
@@ -4232,10 +4244,10 @@
         <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>81</v>
@@ -4246,10 +4258,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4272,13 +4284,13 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4329,7 +4341,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4356,10 +4368,10 @@
         <v>81</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>81</v>
@@ -4370,10 +4382,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4396,16 +4408,16 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4455,7 +4467,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4482,10 +4494,10 @@
         <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>81</v>
@@ -4496,10 +4508,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4525,13 +4537,13 @@
         <v>190</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4561,7 +4573,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>81</v>
@@ -4579,7 +4591,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4588,31 +4600,31 @@
         <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>81</v>
@@ -4620,10 +4632,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4649,13 +4661,13 @@
         <v>190</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4685,7 +4697,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -4703,7 +4715,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4712,42 +4724,42 @@
         <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4773,13 +4785,13 @@
         <v>190</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4808,16 +4820,16 @@
         <v>195</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4827,7 +4839,7 @@
         <v>142</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4851,16 +4863,16 @@
         <v>81</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>81</v>
@@ -4868,13 +4880,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>81</v>
@@ -4899,13 +4911,13 @@
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4916,7 +4928,7 @@
         <v>81</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>81</v>
@@ -4935,7 +4947,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4953,7 +4965,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4968,7 +4980,7 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
@@ -4977,16 +4989,16 @@
         <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>81</v>
@@ -4994,13 +5006,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>81</v>
@@ -5025,13 +5037,13 @@
         <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5042,7 +5054,7 @@
         <v>81</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>81</v>
@@ -5060,28 +5072,28 @@
         <v>195</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5105,16 +5117,16 @@
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>81</v>
@@ -5122,10 +5134,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5151,13 +5163,13 @@
         <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5186,28 +5198,28 @@
         <v>117</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5231,31 +5243,31 @@
         <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5277,14 +5289,14 @@
         <v>190</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5312,10 +5324,10 @@
         <v>195</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5333,7 +5345,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5348,36 +5360,36 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5498,10 +5510,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5624,10 +5636,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5650,19 +5662,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5711,7 +5723,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5738,10 +5750,10 @@
         <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>81</v>
@@ -5752,10 +5764,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5876,10 +5888,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6002,10 +6014,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6019,7 +6031,7 @@
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>81</v>
@@ -6031,16 +6043,16 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -6050,7 +6062,7 @@
         <v>81</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>81</v>
@@ -6089,7 +6101,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6104,7 +6116,7 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>81</v>
+        <v>325</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -6116,10 +6128,10 @@
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>81</v>
@@ -6130,10 +6142,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6159,13 +6171,13 @@
         <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6215,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6242,10 +6254,10 @@
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>81</v>
@@ -6256,10 +6268,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6285,14 +6297,14 @@
         <v>113</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6341,7 +6353,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6356,10 +6368,10 @@
         <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -6368,10 +6380,10 @@
         <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>81</v>
@@ -6382,10 +6394,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6411,14 +6423,14 @@
         <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6467,7 +6479,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6494,10 +6506,10 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>81</v>
@@ -6508,10 +6520,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6534,19 +6546,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6595,7 +6607,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6622,10 +6634,10 @@
         <v>81</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6636,10 +6648,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6665,16 +6677,16 @@
         <v>169</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6723,7 +6735,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6738,10 +6750,10 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
@@ -6750,10 +6762,10 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>81</v>
@@ -6764,10 +6776,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6793,13 +6805,13 @@
         <v>190</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6825,31 +6837,31 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6873,31 +6885,31 @@
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6916,17 +6928,17 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6975,7 +6987,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>93</v>
@@ -6990,25 +7002,25 @@
         <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>81</v>
@@ -7016,10 +7028,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7042,16 +7054,16 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7101,7 +7113,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7122,19 +7134,19 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>81</v>
@@ -7142,10 +7154,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7168,16 +7180,16 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7215,7 +7227,7 @@
         <v>81</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7225,7 +7237,7 @@
         <v>142</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7246,19 +7258,19 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>81</v>
@@ -7266,13 +7278,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>81</v>
@@ -7294,16 +7306,16 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7353,7 +7365,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7368,25 +7380,25 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>81</v>
@@ -7394,10 +7406,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7420,16 +7432,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7467,7 +7479,7 @@
         <v>81</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -7477,7 +7489,7 @@
         <v>142</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7486,7 +7498,7 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>105</v>
@@ -7507,10 +7519,10 @@
         <v>81</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>81</v>
@@ -7518,13 +7530,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>81</v>
@@ -7546,16 +7558,16 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7605,7 +7617,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7614,31 +7626,31 @@
         <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AQ45" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>81</v>
@@ -7646,10 +7658,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7672,13 +7684,13 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7729,7 +7741,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7744,10 +7756,10 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7756,13 +7768,13 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>81</v>
@@ -7770,10 +7782,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7796,13 +7808,13 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7853,7 +7865,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7868,10 +7880,10 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7883,10 +7895,10 @@
         <v>81</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>81</v>
@@ -7894,10 +7906,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7920,13 +7932,13 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7977,7 +7989,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8004,13 +8016,13 @@
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>81</v>
@@ -8018,10 +8030,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8044,13 +8056,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8101,7 +8113,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8113,7 +8125,7 @@
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -8131,7 +8143,7 @@
         <v>81</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>81</v>
@@ -8142,10 +8154,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8266,10 +8278,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8392,14 +8404,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8421,10 +8433,10 @@
         <v>138</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>156</v>
@@ -8479,7 +8491,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8520,10 +8532,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8549,10 +8561,10 @@
         <v>190</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8579,31 +8591,31 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="Z53" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8612,7 +8624,7 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8627,13 +8639,13 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>81</v>
@@ -8644,10 +8656,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8670,13 +8682,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8727,7 +8739,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8736,7 +8748,7 @@
         <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>105</v>
@@ -8757,7 +8769,7 @@
         <v>81</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>81</v>
@@ -8768,10 +8780,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8797,10 +8809,10 @@
         <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8827,31 +8839,31 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="Z55" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8881,7 +8893,7 @@
         <v>81</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>81</v>
@@ -8892,10 +8904,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8918,16 +8930,16 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8977,7 +8989,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -8989,7 +9001,7 @@
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>81</v>
@@ -9007,7 +9019,7 @@
         <v>81</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>81</v>
@@ -9018,10 +9030,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9142,10 +9154,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9268,14 +9280,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9297,10 +9309,10 @@
         <v>138</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>156</v>
@@ -9355,7 +9367,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9396,10 +9408,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9425,10 +9437,10 @@
         <v>190</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9455,31 +9467,31 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="Z60" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9488,7 +9500,7 @@
         <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9500,19 +9512,19 @@
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>81</v>
@@ -9520,10 +9532,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9546,13 +9558,13 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9603,7 +9615,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9612,7 +9624,7 @@
         <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9633,10 +9645,10 @@
         <v>81</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>81</v>
@@ -9644,10 +9656,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9670,13 +9682,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9727,7 +9739,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9748,16 +9760,16 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2512" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -947,12 +947,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-condition-code</t>
-  </si>
-  <si>
-    <t>365: source value from PROBLEM - DIAGNOSIS &gt; ICD DIAGNOSIS (9000011-.01 &gt; 80-)</t>
-  </si>
-  <si>
-    <t>Outpat.ProblemList.ICDIEN</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1016,12 +1010,33 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
+    <t>Condition.code.coding:va-icd</t>
+  </si>
+  <si>
+    <t>va-icd</t>
+  </si>
+  <si>
+    <t>365: source value from PROBLEM - DIAGNOSIS &gt; ICD DIAGNOSIS (9000011-.01 &gt; 80-)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.ICDIEN</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:va-icd.id</t>
+  </si>
+  <si>
     <t>Condition.code.coding.id</t>
   </si>
   <si>
+    <t>Condition.code.coding:va-icd.extension</t>
+  </si>
+  <si>
     <t>Condition.code.coding.extension</t>
   </si>
   <si>
+    <t>Condition.code.coding:va-icd.system</t>
+  </si>
+  <si>
     <t>Condition.code.coding.system</t>
   </si>
   <si>
@@ -1037,13 +1052,13 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://snomed.info/sct</t>
+    <t>urn:see-termmap-in-mapParameter</t>
   </si>
   <si>
     <t>Coding.system</t>
   </si>
   <si>
-    <t>366-1: fixed value = http://snomed.info/sct</t>
+    <t>365-1: fixed value = urn:see-termmap-in-mapParameter</t>
   </si>
   <si>
     <t>C*E.3</t>
@@ -1052,6 +1067,9 @@
     <t>./codeSystem</t>
   </si>
   <si>
+    <t>Condition.code.coding:va-icd.version</t>
+  </si>
+  <si>
     <t>Condition.code.coding.version</t>
   </si>
   <si>
@@ -1073,6 +1091,9 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
+    <t>Condition.code.coding:va-icd.code</t>
+  </si>
+  <si>
     <t>Condition.code.coding.code</t>
   </si>
   <si>
@@ -1088,10 +1109,11 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>366: source value from PROBLEM - SNOMED CT CONCEPT CODE (9000011-80001)</t>
-  </si>
-  <si>
-    <t>Outpat.ProblemList.SNOMEDCTConceptCode</t>
+    <t>365-2: source value from PROBLEM - DIAGNOSIS &gt; ICD DIAGNOSIS - CODE NUMBER (9000011-.01 &gt; 80-.01)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.ICDIEN
+Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1100,6 +1122,9 @@
     <t>./code</t>
   </si>
   <si>
+    <t>Condition.code.coding:va-icd.display</t>
+  </si>
+  <si>
     <t>Condition.code.coding.display</t>
   </si>
   <si>
@@ -1119,6 +1144,9 @@
   </si>
   <si>
     <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:va-icd.userSelected</t>
   </si>
   <si>
     <t>Condition.code.coding.userSelected</t>
@@ -1147,6 +1175,45 @@
   </si>
   <si>
     <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:va-sct</t>
+  </si>
+  <si>
+    <t>va-sct</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:va-sct.id</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:va-sct.extension</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:va-sct.system</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>366-1: fixed value = http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:va-sct.version</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:va-sct.code</t>
+  </si>
+  <si>
+    <t>366: source value from PROBLEM - SNOMED CT CONCEPT CODE (9000011-80001)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.SNOMEDCTConceptCode</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:va-sct.display</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:va-sct.userSelected</t>
   </si>
   <si>
     <t>Condition.code.text</t>
@@ -1928,7 +1995,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR62"/>
+  <dimension ref="A1:AR71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.5390625" customWidth="true" bestFit="true"/>
@@ -1966,7 +2033,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="94.44140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="100.625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
@@ -5360,36 +5427,36 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AQ27" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AP27" t="s" s="2">
+      <c r="AR27" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AR27" t="s" s="2">
-        <v>304</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5510,10 +5577,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5636,10 +5703,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5662,19 +5729,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5711,19 +5778,17 @@
         <v>81</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5750,10 +5815,10 @@
         <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>81</v>
@@ -5764,12 +5829,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5781,25 +5848,29 @@
         <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>169</v>
+        <v>306</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>170</v>
+        <v>307</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5847,25 +5918,25 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>172</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>81</v>
@@ -5874,10 +5945,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>81</v>
+        <v>312</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>173</v>
+        <v>313</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -5888,21 +5959,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
@@ -5914,17 +5985,15 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5961,31 +6030,31 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>81</v>
@@ -6014,46 +6083,44 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>175</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>320</v>
+        <v>176</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
@@ -6062,7 +6129,7 @@
         <v>81</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>323</v>
+        <v>81</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>81</v>
@@ -6089,34 +6156,34 @@
         <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>324</v>
+        <v>178</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -6128,10 +6195,10 @@
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>327</v>
+        <v>173</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>81</v>
@@ -6142,10 +6209,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6159,7 +6226,7 @@
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>81</v>
@@ -6168,18 +6235,20 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6188,7 +6257,7 @@
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>81</v>
+        <v>328</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -6227,7 +6296,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6242,7 +6311,7 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>81</v>
+        <v>330</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
@@ -6254,10 +6323,10 @@
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>81</v>
@@ -6268,10 +6337,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6285,7 +6354,7 @@
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>81</v>
@@ -6294,18 +6363,18 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>338</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6353,7 +6422,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6368,22 +6437,22 @@
         <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>81</v>
@@ -6394,10 +6463,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6411,7 +6480,7 @@
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>81</v>
@@ -6420,17 +6489,17 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6479,7 +6548,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6494,10 +6563,10 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>81</v>
@@ -6523,7 +6592,7 @@
         <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6546,7 +6615,7 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>352</v>
+        <v>169</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>353</v>
@@ -6554,11 +6623,9 @@
       <c r="M37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6607,7 +6674,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6634,10 +6701,10 @@
         <v>81</v>
       </c>
       <c r="AO37" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6648,7 +6715,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>360</v>
@@ -6665,7 +6732,7 @@
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>81</v>
@@ -6674,19 +6741,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>169</v>
+        <v>361</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6735,7 +6802,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6750,22 +6817,22 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>81</v>
@@ -6776,12 +6843,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="B39" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6790,7 +6859,7 @@
         <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6802,18 +6871,20 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>371</v>
+        <v>307</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>372</v>
+        <v>308</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6837,13 +6908,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>375</v>
+        <v>81</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6861,7 +6932,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6885,61 +6956,59 @@
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>377</v>
+        <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>81</v>
+        <v>312</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>378</v>
+        <v>313</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>379</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>319</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>382</v>
+        <v>169</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>383</v>
+        <v>170</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>384</v>
+        <v>171</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>385</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6987,10 +7056,10 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>380</v>
+        <v>172</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>93</v>
@@ -6999,28 +7068,28 @@
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>387</v>
+        <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>390</v>
+        <v>173</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>391</v>
+        <v>81</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>81</v>
@@ -7028,21 +7097,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>392</v>
+        <v>321</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -7051,19 +7120,19 @@
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>393</v>
+        <v>138</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>394</v>
+        <v>175</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>395</v>
+        <v>176</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>396</v>
+        <v>156</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7101,31 +7170,31 @@
         <v>81</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>392</v>
+        <v>178</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>81</v>
@@ -7134,19 +7203,19 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>397</v>
+        <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>398</v>
+        <v>81</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>399</v>
+        <v>173</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>400</v>
+        <v>81</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>81</v>
@@ -7154,10 +7223,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>401</v>
+        <v>323</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7180,18 +7249,20 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>402</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>403</v>
+        <v>324</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>404</v>
+        <v>325</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7200,7 +7271,7 @@
         <v>81</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>81</v>
+        <v>374</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>81</v>
@@ -7227,17 +7298,19 @@
         <v>81</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>401</v>
+        <v>329</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7252,25 +7325,25 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>81</v>
+        <v>375</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>408</v>
+        <v>331</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>410</v>
+        <v>81</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>81</v>
@@ -7278,14 +7351,12 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>411</v>
+        <v>376</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>81</v>
       </c>
@@ -7297,7 +7368,7 @@
         <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>81</v>
@@ -7306,16 +7377,16 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>413</v>
+        <v>169</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>403</v>
+        <v>335</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>404</v>
+        <v>336</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>405</v>
+        <v>337</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7365,7 +7436,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7380,25 +7451,25 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>408</v>
+        <v>339</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>409</v>
+        <v>340</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>410</v>
+        <v>81</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>81</v>
@@ -7406,10 +7477,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>416</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>416</v>
+        <v>342</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7429,21 +7500,21 @@
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>402</v>
+        <v>113</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>417</v>
+        <v>343</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7479,17 +7550,19 @@
         <v>81</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>416</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7498,16 +7571,16 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>420</v>
+        <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>81</v>
+        <v>378</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
@@ -7516,13 +7589,13 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>81</v>
+        <v>349</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>421</v>
+        <v>350</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>81</v>
@@ -7530,14 +7603,12 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>423</v>
+        <v>380</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7549,27 +7620,27 @@
         <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J45" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K45" t="s" s="2">
-        <v>413</v>
+        <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>417</v>
+        <v>353</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7617,7 +7688,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>416</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7626,16 +7697,16 @@
         <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>420</v>
+        <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>426</v>
+        <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -7644,13 +7715,13 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>81</v>
+        <v>357</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>421</v>
+        <v>358</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>81</v>
@@ -7658,10 +7729,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>427</v>
+        <v>381</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>427</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7675,7 +7746,7 @@
         <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
@@ -7684,16 +7755,20 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>413</v>
+        <v>361</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>428</v>
+        <v>362</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7741,7 +7816,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>427</v>
+        <v>366</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7756,10 +7831,10 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7768,13 +7843,13 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>432</v>
+        <v>367</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>433</v>
+        <v>368</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>434</v>
+        <v>81</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>81</v>
@@ -7782,10 +7857,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>435</v>
+        <v>382</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>435</v>
+        <v>382</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7808,16 +7883,20 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>436</v>
+        <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>437</v>
+        <v>383</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7865,7 +7944,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>435</v>
+        <v>387</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7880,10 +7959,10 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>439</v>
+        <v>388</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7892,13 +7971,13 @@
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>441</v>
+        <v>391</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>81</v>
@@ -7906,10 +7985,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7920,7 +7999,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7932,15 +8011,17 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>436</v>
+        <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>444</v>
+        <v>393</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7965,13 +8046,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>81</v>
+        <v>396</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>81</v>
+        <v>397</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>81</v>
+        <v>398</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7989,13 +8070,13 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
@@ -8013,59 +8094,61 @@
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>81</v>
+        <v>399</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>449</v>
+        <v>402</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>449</v>
+        <v>402</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>450</v>
+        <v>404</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>451</v>
+        <v>405</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>452</v>
+        <v>406</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -8113,40 +8196,40 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>449</v>
+        <v>402</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>453</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>81</v>
+        <v>411</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>454</v>
+        <v>412</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>81</v>
+        <v>413</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>81</v>
@@ -8154,10 +8237,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>455</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>455</v>
+        <v>414</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8177,18 +8260,20 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>169</v>
+        <v>415</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>170</v>
+        <v>416</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8237,7 +8322,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>172</v>
+        <v>414</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8249,7 +8334,7 @@
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
@@ -8258,19 +8343,19 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>173</v>
+        <v>421</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>81</v>
@@ -8278,42 +8363,42 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>138</v>
+        <v>424</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>175</v>
+        <v>425</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>176</v>
+        <v>426</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>156</v>
+        <v>427</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8351,31 +8436,29 @@
         <v>81</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>178</v>
+        <v>423</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>81</v>
@@ -8384,19 +8467,19 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>81</v>
+        <v>429</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>173</v>
+        <v>431</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>81</v>
@@ -8404,46 +8487,46 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="D52" t="s" s="2">
-        <v>458</v>
+        <v>81</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>138</v>
+        <v>435</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>459</v>
+        <v>425</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>460</v>
+        <v>426</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8491,40 +8574,40 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>423</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>81</v>
+        <v>429</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>136</v>
+        <v>431</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>81</v>
@@ -8532,10 +8615,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8549,7 +8632,7 @@
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>81</v>
@@ -8558,15 +8641,17 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>190</v>
+        <v>424</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8591,31 +8676,29 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>465</v>
+        <v>81</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>466</v>
+        <v>81</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8624,7 +8707,7 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8639,16 +8722,16 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>468</v>
+        <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>302</v>
+        <v>443</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>81</v>
@@ -8656,12 +8739,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="D54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8670,10 +8755,10 @@
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>81</v>
@@ -8682,15 +8767,17 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>470</v>
+        <v>435</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>471</v>
+        <v>439</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8739,25 +8826,25 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>469</v>
+        <v>438</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -8769,10 +8856,10 @@
         <v>81</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>81</v>
@@ -8780,10 +8867,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>474</v>
+        <v>449</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>474</v>
+        <v>449</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8797,22 +8884,22 @@
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>190</v>
+        <v>435</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>476</v>
+        <v>451</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8839,13 +8926,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>477</v>
+        <v>81</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>478</v>
+        <v>81</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8863,7 +8950,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>474</v>
+        <v>449</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8878,10 +8965,10 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>81</v>
+        <v>452</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>81</v>
+        <v>453</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
@@ -8890,13 +8977,13 @@
         <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>81</v>
+        <v>454</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>81</v>
+        <v>456</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>81</v>
@@ -8904,10 +8991,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8918,29 +9005,27 @@
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8989,25 +9074,25 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>484</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>81</v>
+        <v>462</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
@@ -9019,10 +9104,10 @@
         <v>81</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>81</v>
+        <v>464</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>81</v>
@@ -9030,10 +9115,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9053,16 +9138,16 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>169</v>
+        <v>458</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>170</v>
+        <v>466</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>171</v>
+        <v>467</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9113,7 +9198,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>172</v>
+        <v>465</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9125,7 +9210,7 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
@@ -9140,13 +9225,13 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>81</v>
+        <v>468</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>173</v>
+        <v>469</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>81</v>
+        <v>470</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>81</v>
@@ -9154,14 +9239,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9180,17 +9265,15 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>138</v>
+        <v>472</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>175</v>
+        <v>473</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -9239,7 +9322,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>178</v>
+        <v>471</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9251,7 +9334,7 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>144</v>
+        <v>475</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
@@ -9269,7 +9352,7 @@
         <v>81</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>173</v>
+        <v>476</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
@@ -9280,46 +9363,42 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>458</v>
+        <v>81</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>459</v>
+        <v>170</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9367,19 +9446,19 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>461</v>
+        <v>172</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9397,7 +9476,7 @@
         <v>81</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>81</v>
@@ -9408,14 +9487,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9431,18 +9510,20 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>490</v>
+        <v>175</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9467,13 +9548,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>492</v>
+        <v>81</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>493</v>
+        <v>81</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9491,7 +9572,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>489</v>
+        <v>178</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9500,10 +9581,10 @@
         <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>494</v>
+        <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>81</v>
@@ -9512,19 +9593,19 @@
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>266</v>
+        <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>496</v>
+        <v>173</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>81</v>
@@ -9532,14 +9613,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>498</v>
+        <v>479</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>498</v>
+        <v>479</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9552,22 +9633,26 @@
         <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>499</v>
+        <v>138</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
       </c>
@@ -9615,7 +9700,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9624,10 +9709,10 @@
         <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>494</v>
+        <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
@@ -9645,10 +9730,10 @@
         <v>81</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>473</v>
+        <v>136</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>81</v>
@@ -9656,10 +9741,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9670,7 +9755,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9682,13 +9767,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>503</v>
+        <v>190</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9715,13 +9800,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>81</v>
+        <v>396</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>81</v>
+        <v>487</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9739,16 +9824,16 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>81</v>
+        <v>489</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9760,26 +9845,1150 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR62" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR63" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR64" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="AN62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO62" t="s" s="2">
+      <c r="AK65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AP62" t="s" s="2">
+      <c r="AQ65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR65" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AQ62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR62" t="s" s="2">
+      <c r="B66" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR66" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR67" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR68" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AR69" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AR70" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AR71" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR62">
+  <autoFilter ref="A1:AR71">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9789,7 +10998,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -654,7 +654,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -663,7 +663,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>345-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>345-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -654,7 +654,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
+    <t>http://va.gov/identifiers/$Sta3n/9000011</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -663,7 +663,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>345-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
+    <t>345-1: fixed value = http://va.gov/identifiers/$Sta3n/9000011</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2834" uniqueCount="522">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1010,6 +1010,139 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
+    <t>Condition.code.coding.id</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>366-1: fixed value = http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>366: source value from PROBLEM - SNOMED CT CONCEPT CODE (9000011-80001)</t>
+  </si>
+  <si>
+    <t>Outpat.ProblemList.SNOMEDCTConceptCode</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
     <t>Condition.code.coding:va-icd</t>
   </si>
   <si>
@@ -1025,88 +1158,22 @@
     <t>Condition.code.coding:va-icd.id</t>
   </si>
   <si>
-    <t>Condition.code.coding.id</t>
-  </si>
-  <si>
     <t>Condition.code.coding:va-icd.extension</t>
   </si>
   <si>
-    <t>Condition.code.coding.extension</t>
-  </si>
-  <si>
     <t>Condition.code.coding:va-icd.system</t>
   </si>
   <si>
-    <t>Condition.code.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
     <t>urn:see-termmap-in-mapParameter</t>
   </si>
   <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
     <t>365-1: fixed value = urn:see-termmap-in-mapParameter</t>
   </si>
   <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
     <t>Condition.code.coding:va-icd.version</t>
   </si>
   <si>
-    <t>Condition.code.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
     <t>Condition.code.coding:va-icd.code</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
   </si>
   <si>
     <t>365-2: source value from PROBLEM - DIAGNOSIS &gt; ICD DIAGNOSIS - CODE NUMBER (9000011-.01 &gt; 80-.01)</t>
@@ -1116,104 +1183,10 @@
 Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
   </si>
   <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
     <t>Condition.code.coding:va-icd.display</t>
   </si>
   <si>
-    <t>Condition.code.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
     <t>Condition.code.coding:va-icd.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:va-sct</t>
-  </si>
-  <si>
-    <t>va-sct</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:va-sct.id</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:va-sct.extension</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:va-sct.system</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>366-1: fixed value = http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:va-sct.version</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:va-sct.code</t>
-  </si>
-  <si>
-    <t>366: source value from PROBLEM - SNOMED CT CONCEPT CODE (9000011-80001)</t>
-  </si>
-  <si>
-    <t>Outpat.ProblemList.SNOMEDCTConceptCode</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:va-sct.display</t>
-  </si>
-  <si>
-    <t>Condition.code.coding:va-sct.userSelected</t>
   </si>
   <si>
     <t>Condition.code.text</t>
@@ -1995,7 +1968,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR71"/>
+  <dimension ref="A1:AR70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.5390625" customWidth="true" bestFit="true"/>
@@ -5832,11 +5805,9 @@
         <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5848,29 +5819,25 @@
         <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>306</v>
+        <v>169</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>307</v>
+        <v>170</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5918,25 +5885,25 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>172</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>316</v>
+        <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>81</v>
@@ -5945,10 +5912,10 @@
         <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>312</v>
+        <v>81</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>313</v>
+        <v>173</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>81</v>
@@ -5959,21 +5926,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
@@ -5985,15 +5952,17 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -6030,31 +5999,31 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>81</v>
@@ -6083,44 +6052,46 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>175</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>176</v>
+        <v>318</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
@@ -6129,7 +6100,7 @@
         <v>81</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>81</v>
+        <v>321</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>81</v>
@@ -6156,34 +6127,34 @@
         <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>178</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -6195,10 +6166,10 @@
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>81</v>
+        <v>324</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>173</v>
+        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>81</v>
@@ -6209,10 +6180,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6226,7 +6197,7 @@
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>81</v>
@@ -6235,20 +6206,18 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6257,7 +6226,7 @@
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>328</v>
+        <v>81</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -6296,7 +6265,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6311,7 +6280,7 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>330</v>
+        <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
@@ -6340,7 +6309,7 @@
         <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6354,7 +6323,7 @@
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>81</v>
@@ -6363,18 +6332,18 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6422,7 +6391,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6437,10 +6406,10 @@
         <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -6449,10 +6418,10 @@
         <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>81</v>
@@ -6463,7 +6432,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>342</v>
@@ -6480,7 +6449,7 @@
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>81</v>
@@ -6489,7 +6458,7 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>343</v>
@@ -6563,22 +6532,22 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>81</v>
@@ -6589,10 +6558,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6615,17 +6584,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>169</v>
+        <v>350</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6674,7 +6645,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6701,10 +6672,10 @@
         <v>81</v>
       </c>
       <c r="AO37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6715,12 +6686,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C38" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="B38" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6732,7 +6705,7 @@
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>81</v>
@@ -6741,19 +6714,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>361</v>
+        <v>306</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>362</v>
+        <v>307</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>363</v>
+        <v>308</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>364</v>
+        <v>309</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>365</v>
+        <v>310</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6802,13 +6775,13 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>366</v>
+        <v>311</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
@@ -6817,10 +6790,10 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>81</v>
+        <v>360</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>81</v>
+        <v>361</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
@@ -6829,10 +6802,10 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>367</v>
+        <v>312</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>368</v>
+        <v>313</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>81</v>
@@ -6843,14 +6816,12 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6868,23 +6839,19 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>306</v>
+        <v>169</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>170</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6932,19 +6899,19 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>311</v>
+        <v>172</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6959,10 +6926,10 @@
         <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>312</v>
+        <v>81</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>313</v>
+        <v>173</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>81</v>
@@ -6973,21 +6940,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6999,15 +6966,17 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -7044,31 +7013,31 @@
         <v>81</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
@@ -7097,44 +7066,46 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>175</v>
+        <v>317</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>176</v>
+        <v>318</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -7143,7 +7114,7 @@
         <v>81</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>81</v>
@@ -7170,34 +7141,34 @@
         <v>81</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>178</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
@@ -7209,10 +7180,10 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>81</v>
+        <v>324</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>173</v>
+        <v>325</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>81</v>
@@ -7223,10 +7194,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7240,7 +7211,7 @@
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>81</v>
@@ -7249,20 +7220,18 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7271,7 +7240,7 @@
         <v>81</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>81</v>
@@ -7310,7 +7279,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7325,7 +7294,7 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>375</v>
+        <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
@@ -7351,10 +7320,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7368,7 +7337,7 @@
         <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>81</v>
@@ -7377,18 +7346,18 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N43" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -7436,7 +7405,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7451,10 +7420,10 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>81</v>
+        <v>369</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>81</v>
+        <v>370</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
@@ -7463,10 +7432,10 @@
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
@@ -7477,7 +7446,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>342</v>
@@ -7494,7 +7463,7 @@
         <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>81</v>
@@ -7503,7 +7472,7 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>343</v>
@@ -7577,10 +7546,10 @@
         <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>378</v>
+        <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>379</v>
+        <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
@@ -7589,10 +7558,10 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7603,10 +7572,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7629,17 +7598,19 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>169</v>
+        <v>350</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7688,7 +7659,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7715,10 +7686,10 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>81</v>
@@ -7729,10 +7700,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7746,7 +7717,7 @@
         <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
@@ -7755,19 +7726,19 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>361</v>
+        <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7816,7 +7787,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7831,10 +7802,10 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7843,10 +7814,10 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>81</v>
@@ -7857,10 +7828,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7871,10 +7842,10 @@
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>81</v>
@@ -7883,20 +7854,18 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O47" t="s" s="2">
         <v>386</v>
       </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7920,13 +7889,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7944,13 +7913,13 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
@@ -7959,19 +7928,19 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>391</v>
@@ -7980,29 +7949,29 @@
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>81</v>
+        <v>394</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>81</v>
@@ -8011,18 +7980,18 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>190</v>
+        <v>395</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -8046,13 +8015,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>396</v>
+        <v>81</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>397</v>
+        <v>81</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>398</v>
+        <v>81</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -8070,13 +8039,13 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
@@ -8085,50 +8054,50 @@
         <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>81</v>
+        <v>399</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>81</v>
+        <v>400</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>399</v>
+        <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>81</v>
+        <v>402</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>401</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>403</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>81</v>
@@ -8137,18 +8106,18 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -8196,10 +8165,10 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>93</v>
@@ -8211,10 +8180,10 @@
         <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>410</v>
@@ -8254,7 +8223,7 @@
         <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>81</v>
@@ -8310,16 +8279,14 @@
         <v>81</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>414</v>
@@ -8343,19 +8310,19 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>81</v>
@@ -8363,12 +8330,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8389,16 +8358,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8436,17 +8405,19 @@
         <v>81</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AC51" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8461,25 +8432,25 @@
         <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>81</v>
+        <v>427</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>81</v>
+        <v>428</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>81</v>
@@ -8487,14 +8458,12 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8512,19 +8481,19 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8562,19 +8531,17 @@
         <v>81</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8583,31 +8550,31 @@
         <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>81</v>
+        <v>433</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>429</v>
+        <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>81</v>
@@ -8615,12 +8582,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8641,16 +8610,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8688,17 +8657,19 @@
         <v>81</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AC53" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8707,16 +8678,16 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -8728,10 +8699,10 @@
         <v>81</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>81</v>
@@ -8739,14 +8710,12 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8764,20 +8733,18 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8826,7 +8793,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8835,31 +8802,31 @@
         <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>81</v>
@@ -8867,10 +8834,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8893,7 +8860,7 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>450</v>
@@ -8950,7 +8917,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8977,13 +8944,13 @@
         <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AP55" t="s" s="2">
+      <c r="AQ55" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>81</v>
@@ -8991,10 +8958,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9008,7 +8975,7 @@
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>81</v>
@@ -9017,13 +8984,13 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9074,7 +9041,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9089,25 +9056,25 @@
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>81</v>
@@ -9115,10 +9082,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9129,7 +9096,7 @@
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -9138,16 +9105,16 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9198,19 +9165,19 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>105</v>
+        <v>466</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
@@ -9225,13 +9192,13 @@
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>468</v>
+        <v>81</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>470</v>
+        <v>81</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>81</v>
@@ -9239,10 +9206,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9253,7 +9220,7 @@
         <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>81</v>
@@ -9265,13 +9232,13 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>472</v>
+        <v>169</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>473</v>
+        <v>170</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>474</v>
+        <v>171</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9322,19 +9289,19 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>471</v>
+        <v>172</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>475</v>
+        <v>81</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
@@ -9352,7 +9319,7 @@
         <v>81</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>476</v>
+        <v>173</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>81</v>
@@ -9363,21 +9330,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
@@ -9389,15 +9356,17 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9446,19 +9415,19 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9487,14 +9456,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>153</v>
+        <v>471</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9507,24 +9476,26 @@
         <v>81</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>175</v>
+        <v>472</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>176</v>
+        <v>473</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="O60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9572,7 +9543,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>178</v>
+        <v>474</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9602,7 +9573,7 @@
         <v>81</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>81</v>
@@ -9613,46 +9584,42 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>480</v>
+        <v>81</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
       </c>
@@ -9676,13 +9643,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>81</v>
+        <v>478</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>81</v>
+        <v>479</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9700,19 +9667,19 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
@@ -9724,13 +9691,13 @@
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>81</v>
+        <v>481</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>136</v>
+        <v>300</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>81</v>
@@ -9741,10 +9708,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9755,7 +9722,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9767,13 +9734,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>190</v>
+        <v>483</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9800,13 +9767,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>396</v>
+        <v>81</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>487</v>
+        <v>81</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9824,16 +9791,16 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9848,13 +9815,13 @@
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>490</v>
+        <v>81</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>300</v>
+        <v>486</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>81</v>
@@ -9865,10 +9832,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9879,7 +9846,7 @@
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9891,13 +9858,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>492</v>
+        <v>190</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9924,13 +9891,13 @@
         <v>81</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>81</v>
+        <v>490</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>81</v>
+        <v>491</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -9948,16 +9915,16 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>489</v>
+        <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>105</v>
@@ -9978,7 +9945,7 @@
         <v>81</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>81</v>
@@ -9989,10 +9956,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10003,7 +9970,7 @@
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -10015,15 +9982,17 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>190</v>
+        <v>463</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -10048,13 +10017,13 @@
         <v>81</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>396</v>
+        <v>81</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>499</v>
+        <v>81</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>500</v>
+        <v>81</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>81</v>
@@ -10072,19 +10041,19 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>105</v>
+        <v>497</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -10102,7 +10071,7 @@
         <v>81</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>81</v>
@@ -10113,10 +10082,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10127,7 +10096,7 @@
         <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -10139,17 +10108,15 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>472</v>
+        <v>169</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>503</v>
+        <v>170</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10198,19 +10165,19 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>502</v>
+        <v>172</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>506</v>
+        <v>81</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>81</v>
@@ -10228,7 +10195,7 @@
         <v>81</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>507</v>
+        <v>173</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>81</v>
@@ -10239,21 +10206,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
@@ -10265,15 +10232,17 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -10322,19 +10291,19 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
@@ -10363,14 +10332,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>153</v>
+        <v>471</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10383,24 +10352,26 @@
         <v>81</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>175</v>
+        <v>472</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>176</v>
+        <v>473</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="O67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
@@ -10448,7 +10419,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>178</v>
+        <v>474</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10478,7 +10449,7 @@
         <v>81</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>81</v>
@@ -10489,14 +10460,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>480</v>
+        <v>81</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10509,26 +10480,22 @@
         <v>81</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
       </c>
@@ -10552,13 +10519,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>81</v>
+        <v>387</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>81</v>
+        <v>506</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10576,7 +10543,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10585,10 +10552,10 @@
         <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>81</v>
@@ -10597,19 +10564,19 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>81</v>
+        <v>508</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>136</v>
+        <v>509</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>81</v>
+        <v>510</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>81</v>
@@ -10643,13 +10610,13 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>190</v>
+        <v>512</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10676,13 +10643,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>396</v>
+        <v>81</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>514</v>
+        <v>81</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>515</v>
+        <v>81</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10709,7 +10676,7 @@
         <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10721,19 +10688,19 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>517</v>
+        <v>81</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>266</v>
+        <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>518</v>
+        <v>486</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>81</v>
@@ -10741,10 +10708,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10764,16 +10731,16 @@
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10824,7 +10791,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -10833,7 +10800,7 @@
         <v>83</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>516</v>
+        <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10845,150 +10812,26 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>81</v>
+        <v>519</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>81</v>
+        <v>520</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>519</v>
+        <v>81</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AR71" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR71">
+  <autoFilter ref="A1:AR70">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10998,7 +10841,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI70">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1256,7 +1256,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1981,7 +1981,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="58.67578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1269,7 +1269,7 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
-    <t>367: reference from PROBLEM - PATIENT NAME (9000011-.02)</t>
+    <t>367: reference from PROBLEM - PATIENT NAME &gt; PATIENT/IHS - NAME (9000011-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.PatientIEN</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1269,7 +1269,7 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
-    <t>367: reference from PROBLEM - PATIENT NAME &gt; PATIENT/IHS - NAME (9000011-.02 &gt; 9000001-.01)</t>
+    <t>367: reference from PROBLEM - PATIENT NAME (9000011-.02)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.PatientIEN</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -758,7 +758,7 @@
     <t>The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFproblemStatus</t>
+    <t>http://va.gov/fhir/ValueSet/problemStatus</t>
   </si>
   <si>
     <t>con-3
@@ -800,7 +800,7 @@
 The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFproblemVerificationStatus</t>
+    <t>http://va.gov/fhir/ValueSet/problemVerificationStatus</t>
   </si>
   <si>
     <t>con-3

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2834" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2834" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -763,6 +763,10 @@
   <si>
     <t>con-3
 con-4con-5</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ConditionProblem-349:if Not Null then fixed value #resolved {null}</t>
   </si>
   <si>
     <t>605: terminologyMaps using VF_problemStatus on PROBLEM - STATUS (9000011-.12)</t>
@@ -4643,28 +4647,28 @@
         <v>240</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>241</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>81</v>
@@ -4672,10 +4676,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4701,13 +4705,13 @@
         <v>190</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4737,7 +4741,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -4755,7 +4759,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4764,42 +4768,42 @@
         <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4825,13 +4829,13 @@
         <v>190</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4860,16 +4864,16 @@
         <v>195</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4879,7 +4883,7 @@
         <v>142</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4903,16 +4907,16 @@
         <v>81</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>81</v>
@@ -4920,13 +4924,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>81</v>
@@ -4951,13 +4955,13 @@
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4968,7 +4972,7 @@
         <v>81</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>81</v>
@@ -4987,7 +4991,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -5005,7 +5009,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5020,7 +5024,7 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
@@ -5029,16 +5033,16 @@
         <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>81</v>
@@ -5046,13 +5050,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>81</v>
@@ -5077,13 +5081,13 @@
         <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5094,7 +5098,7 @@
         <v>81</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>81</v>
@@ -5112,10 +5116,10 @@
         <v>195</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -5133,7 +5137,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5157,16 +5161,16 @@
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>81</v>
@@ -5174,10 +5178,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5203,13 +5207,13 @@
         <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5238,10 +5242,10 @@
         <v>117</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5259,7 +5263,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5283,31 +5287,31 @@
         <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5329,14 +5333,14 @@
         <v>190</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5364,10 +5368,10 @@
         <v>195</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5385,7 +5389,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5406,30 +5410,30 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5550,10 +5554,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5676,10 +5680,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5702,19 +5706,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5751,7 +5755,7 @@
         <v>81</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
@@ -5761,7 +5765,7 @@
         <v>142</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5788,10 +5792,10 @@
         <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>81</v>
@@ -5802,10 +5806,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5926,10 +5930,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6052,10 +6056,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6081,16 +6085,16 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -6100,7 +6104,7 @@
         <v>81</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>81</v>
@@ -6139,7 +6143,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6154,7 +6158,7 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -6166,10 +6170,10 @@
         <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>81</v>
@@ -6180,10 +6184,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6209,13 +6213,13 @@
         <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6265,7 +6269,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6292,10 +6296,10 @@
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>81</v>
@@ -6306,10 +6310,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6335,14 +6339,14 @@
         <v>113</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6391,7 +6395,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6406,10 +6410,10 @@
         <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -6418,10 +6422,10 @@
         <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>81</v>
@@ -6432,10 +6436,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6461,14 +6465,14 @@
         <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6517,7 +6521,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6544,10 +6548,10 @@
         <v>81</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>81</v>
@@ -6558,10 +6562,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6584,19 +6588,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6645,7 +6649,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6672,10 +6676,10 @@
         <v>81</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>81</v>
@@ -6686,13 +6690,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>81</v>
@@ -6714,19 +6718,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6775,7 +6779,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6790,10 +6794,10 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
@@ -6802,10 +6806,10 @@
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>81</v>
@@ -6816,10 +6820,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6940,10 +6944,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7066,10 +7070,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7095,16 +7099,16 @@
         <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -7114,7 +7118,7 @@
         <v>81</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>81</v>
@@ -7153,7 +7157,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7168,7 +7172,7 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
@@ -7180,10 +7184,10 @@
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>81</v>
@@ -7194,10 +7198,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7223,13 +7227,13 @@
         <v>169</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7279,7 +7283,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7306,10 +7310,10 @@
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>81</v>
@@ -7320,10 +7324,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7349,14 +7353,14 @@
         <v>113</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7405,7 +7409,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7420,10 +7424,10 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
@@ -7432,10 +7436,10 @@
         <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>81</v>
@@ -7446,10 +7450,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7475,14 +7479,14 @@
         <v>169</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7531,7 +7535,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7558,10 +7562,10 @@
         <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>81</v>
@@ -7572,10 +7576,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7598,19 +7602,19 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7659,7 +7663,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7686,10 +7690,10 @@
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>81</v>
@@ -7700,10 +7704,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7729,16 +7733,16 @@
         <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7787,7 +7791,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7802,10 +7806,10 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7814,10 +7818,10 @@
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>81</v>
@@ -7828,10 +7832,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7857,13 +7861,13 @@
         <v>190</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7889,13 +7893,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7913,7 +7917,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7937,31 +7941,31 @@
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7980,17 +7984,17 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8039,7 +8043,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>93</v>
@@ -8054,25 +8058,25 @@
         <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>81</v>
@@ -8080,10 +8084,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8106,16 +8110,16 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8165,7 +8169,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8186,19 +8190,19 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>81</v>
@@ -8206,10 +8210,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8232,16 +8236,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8279,7 +8283,7 @@
         <v>81</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8289,7 +8293,7 @@
         <v>142</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8310,19 +8314,19 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>81</v>
@@ -8330,13 +8334,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>81</v>
@@ -8358,16 +8362,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8417,7 +8421,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8432,25 +8436,25 @@
         <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>81</v>
@@ -8458,10 +8462,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8484,16 +8488,16 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8531,7 +8535,7 @@
         <v>81</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
@@ -8541,7 +8545,7 @@
         <v>142</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8550,7 +8554,7 @@
         <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>105</v>
@@ -8571,10 +8575,10 @@
         <v>81</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>81</v>
@@ -8582,13 +8586,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>81</v>
@@ -8610,16 +8614,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8669,7 +8673,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8678,16 +8682,16 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -8699,10 +8703,10 @@
         <v>81</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>81</v>
@@ -8710,10 +8714,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8736,13 +8740,13 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8793,7 +8797,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8808,10 +8812,10 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -8820,13 +8824,13 @@
         <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>81</v>
@@ -8834,10 +8838,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8860,13 +8864,13 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8917,7 +8921,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8932,10 +8936,10 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
@@ -8947,10 +8951,10 @@
         <v>81</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>81</v>
@@ -8958,10 +8962,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8984,13 +8988,13 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9041,7 +9045,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9068,13 +9072,13 @@
         <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>81</v>
@@ -9082,10 +9086,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9108,13 +9112,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9165,7 +9169,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9177,7 +9181,7 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
@@ -9195,7 +9199,7 @@
         <v>81</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>81</v>
@@ -9206,10 +9210,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9330,10 +9334,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9456,14 +9460,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9485,10 +9489,10 @@
         <v>138</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>156</v>
@@ -9543,7 +9547,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9584,10 +9588,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9613,10 +9617,10 @@
         <v>190</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9643,13 +9647,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9667,7 +9671,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9676,7 +9680,7 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9691,13 +9695,13 @@
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>81</v>
@@ -9708,10 +9712,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9734,13 +9738,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9791,7 +9795,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9800,7 +9804,7 @@
         <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9821,7 +9825,7 @@
         <v>81</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>81</v>
@@ -9832,10 +9836,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9861,10 +9865,10 @@
         <v>190</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9891,13 +9895,13 @@
         <v>81</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -9915,7 +9919,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -9945,7 +9949,7 @@
         <v>81</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>81</v>
@@ -9956,10 +9960,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9982,16 +9986,16 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10041,7 +10045,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10053,7 +10057,7 @@
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -10071,7 +10075,7 @@
         <v>81</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>81</v>
@@ -10082,10 +10086,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10206,10 +10210,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10332,14 +10336,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10361,10 +10365,10 @@
         <v>138</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>156</v>
@@ -10419,7 +10423,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10460,10 +10464,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10489,10 +10493,10 @@
         <v>190</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10519,13 +10523,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10543,7 +10547,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10552,7 +10556,7 @@
         <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10564,19 +10568,19 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>81</v>
@@ -10584,10 +10588,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10610,13 +10614,13 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10667,7 +10671,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10676,7 +10680,7 @@
         <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10697,10 +10701,10 @@
         <v>81</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>81</v>
@@ -10708,10 +10712,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10734,13 +10738,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10791,7 +10795,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -10812,16 +10816,16 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -766,7 +766,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ConditionProblem-349:if Not Null then fixed value #resolved {null}</t>
+cp-16-349:9000011-1.07: if Not Null then #resolved {null}</t>
   </si>
   <si>
     <t>605: terminologyMaps using VF_problemStatus on PROBLEM - STATUS (9000011-.12)</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2039,7 +2039,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="100.625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="68.20703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -778,7 +778,7 @@
     <t>Outpat.ProblemList.ActiveFlag</t>
   </si>
   <si>
-    <t>problem.status</t>
+    <t>Problem.ProblemExtension.Status</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -823,7 +823,7 @@
     <t>Outpat.ProblemList.ProblemListCondition</t>
   </si>
   <si>
-    <t>problem.removed,problem.unverified</t>
+    <t>Problem.ProblemExtension.IsRemoved,Problem.ProblemExtension.IsVerified,Problem.ProblemExtension.Removed</t>
   </si>
   <si>
     <t>&lt; 410514004 |Finding context value|</t>
@@ -1101,7 +1101,7 @@
     <t>Outpat.ProblemList.SNOMEDCTConceptCode</t>
   </si>
   <si>
-    <t>problem.sctc,problem.sctt</t>
+    <t>Problem.ProblemExtension.Problem</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1171,9 +1171,6 @@
     <t>Outpat.ProblemList.ICDIEN</t>
   </si>
   <si>
-    <t>problem.icd,problem.icdd</t>
-  </si>
-  <si>
     <t>Condition.code.coding:va-icd.id</t>
   </si>
   <si>
@@ -1232,7 +1229,7 @@
     <t>Outpat.ProblemList.ProviderNarrativeIEN</t>
   </si>
   <si>
-    <t>problem.name</t>
+    <t>Problem.ProblemExtension.ProblemDetails</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -1385,7 +1382,7 @@
     <t>Outpat.ProblemList.OnsetDateTime</t>
   </si>
   <si>
-    <t>problem.onset</t>
+    <t>Problem.ProblemExtension.FromTime,Problem.ProblemExtension.OnsetDate</t>
   </si>
   <si>
     <t>Condition.abatement[x]</t>
@@ -1422,7 +1419,7 @@
     <t>Outpat.ProblemList.ResolvedDateTime</t>
   </si>
   <si>
-    <t>problem.resolved</t>
+    <t>Problem.ProblemExtension.ToTime</t>
   </si>
   <si>
     <t>Condition.recordedDate</t>
@@ -1440,7 +1437,7 @@
     <t>Outpat.ProblemList.EnteredDateTime</t>
   </si>
   <si>
-    <t>problem.entered</t>
+    <t>Problem.EnteredOn</t>
   </si>
   <si>
     <t>REL-11</t>
@@ -2039,7 +2036,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="100.625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="105.5703125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="68.20703125" customWidth="true" bestFit="true"/>
@@ -6939,7 +6936,7 @@
         <v>366</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
@@ -6962,7 +6959,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>318</v>
@@ -7089,7 +7086,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>319</v>
@@ -7218,7 +7215,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>320</v>
@@ -7266,7 +7263,7 @@
         <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>82</v>
@@ -7320,7 +7317,7 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
@@ -7349,7 +7346,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>330</v>
@@ -7478,7 +7475,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>337</v>
@@ -7578,13 +7575,13 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>376</v>
-      </c>
       <c r="AM43" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -7607,7 +7604,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>347</v>
@@ -7736,7 +7733,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>354</v>
@@ -7867,10 +7864,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7896,16 +7893,16 @@
         <v>170</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7954,7 +7951,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -7969,25 +7966,25 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>82</v>
@@ -7998,10 +7995,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8027,13 +8024,13 @@
         <v>191</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8059,14 +8056,14 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="Y47" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="Y47" t="s" s="2">
+      <c r="Z47" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8083,7 +8080,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8110,31 +8107,31 @@
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AP47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
+      <c r="AR47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS47" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS47" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8153,17 +8150,17 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8212,7 +8209,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>94</v>
@@ -8227,28 +8224,28 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AM48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AO48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP48" t="s" s="2">
+      <c r="AQ48" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AQ48" t="s" s="2">
+      <c r="AR48" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AS48" t="s" s="2">
         <v>82</v>
@@ -8256,10 +8253,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8282,16 +8279,16 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8341,7 +8338,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8365,19 +8362,19 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AO49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP49" t="s" s="2">
+      <c r="AQ49" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AQ49" t="s" s="2">
+      <c r="AR49" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
@@ -8385,10 +8382,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8411,16 +8408,16 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8458,7 +8455,7 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8468,7 +8465,7 @@
         <v>143</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8492,19 +8489,19 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AO50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AQ50" t="s" s="2">
+      <c r="AR50" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AS50" t="s" s="2">
         <v>82</v>
@@ -8512,13 +8509,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>82</v>
@@ -8540,16 +8537,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8599,7 +8596,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8614,28 +8611,28 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>436</v>
-      </c>
       <c r="AN51" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AO51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP51" t="s" s="2">
+      <c r="AQ51" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AQ51" t="s" s="2">
+      <c r="AR51" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>82</v>
@@ -8643,10 +8640,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8669,16 +8666,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8716,7 +8713,7 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
@@ -8726,7 +8723,7 @@
         <v>143</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -8735,7 +8732,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8759,10 +8756,10 @@
         <v>82</v>
       </c>
       <c r="AQ52" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AR52" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AR52" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AS52" t="s" s="2">
         <v>82</v>
@@ -8770,13 +8767,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>82</v>
@@ -8798,16 +8795,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8857,7 +8854,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -8866,20 +8863,20 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AM53" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8890,10 +8887,10 @@
         <v>82</v>
       </c>
       <c r="AQ53" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AR53" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AR53" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AS53" t="s" s="2">
         <v>82</v>
@@ -8901,10 +8898,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8927,13 +8924,13 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8984,7 +8981,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -8999,28 +8996,28 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AM54" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AN54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP54" t="s" s="2">
+      <c r="AQ54" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AQ54" t="s" s="2">
+      <c r="AR54" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AR54" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AS54" t="s" s="2">
         <v>82</v>
@@ -9028,10 +9025,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9054,13 +9051,13 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9111,7 +9108,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9126,28 +9123,28 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AM55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
+      <c r="AR55" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AR55" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AS55" t="s" s="2">
         <v>82</v>
@@ -9155,10 +9152,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9181,13 +9178,13 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9238,7 +9235,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9268,13 +9265,13 @@
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AQ56" t="s" s="2">
+      <c r="AR56" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AR56" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AS56" t="s" s="2">
         <v>82</v>
@@ -9282,10 +9279,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9308,13 +9305,13 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9365,7 +9362,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9377,28 +9374,28 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ57" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>82</v>
@@ -9409,10 +9406,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9536,10 +9533,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9665,14 +9662,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9694,10 +9691,10 @@
         <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>157</v>
@@ -9752,7 +9749,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -9796,10 +9793,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9825,10 +9822,10 @@
         <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9855,14 +9852,14 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>489</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9879,7 +9876,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -9888,7 +9885,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9906,7 +9903,7 @@
         <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>248</v>
@@ -9923,10 +9920,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9949,13 +9946,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10006,7 +10003,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10015,7 +10012,7 @@
         <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10039,7 +10036,7 @@
         <v>82</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>82</v>
@@ -10050,10 +10047,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10079,10 +10076,10 @@
         <v>191</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10109,14 +10106,14 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>501</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10133,7 +10130,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10166,7 +10163,7 @@
         <v>82</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>82</v>
@@ -10177,10 +10174,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10203,16 +10200,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10262,7 +10259,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10274,28 +10271,28 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>82</v>
@@ -10306,10 +10303,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10433,10 +10430,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10562,14 +10559,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10591,10 +10588,10 @@
         <v>139</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>157</v>
@@ -10649,7 +10646,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -10693,10 +10690,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10722,10 +10719,10 @@
         <v>191</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10752,14 +10749,14 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10776,7 +10773,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -10785,7 +10782,7 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>106</v>
@@ -10800,7 +10797,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>270</v>
@@ -10809,10 +10806,10 @@
         <v>82</v>
       </c>
       <c r="AQ68" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AR68" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>82</v>
@@ -10820,10 +10817,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10846,13 +10843,13 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10903,7 +10900,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -10912,7 +10909,7 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>106</v>
@@ -10936,10 +10933,10 @@
         <v>82</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AS69" t="s" s="2">
         <v>82</v>
@@ -10947,10 +10944,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10973,13 +10970,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11030,7 +11027,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11054,16 +11051,16 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AO70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -778,7 +778,7 @@
     <t>Outpat.ProblemList.ActiveFlag</t>
   </si>
   <si>
-    <t>Problem.ProblemExtension.Status</t>
+    <t>Problem.Extension[ProblemExtension].Status</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -823,7 +823,7 @@
     <t>Outpat.ProblemList.ProblemListCondition</t>
   </si>
   <si>
-    <t>Problem.ProblemExtension.IsRemoved,Problem.ProblemExtension.IsVerified,Problem.ProblemExtension.Removed</t>
+    <t>Problem.Extension[ProblemExtension].IsRemoved,Problem.Extension[ProblemExtension].IsVerified,Problem.Extension[ProblemExtension].Removed</t>
   </si>
   <si>
     <t>&lt; 410514004 |Finding context value|</t>
@@ -1101,7 +1101,7 @@
     <t>Outpat.ProblemList.SNOMEDCTConceptCode</t>
   </si>
   <si>
-    <t>Problem.ProblemExtension.Problem</t>
+    <t>Problem.Extension[ProblemExtension].Problem</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1229,7 +1229,7 @@
     <t>Outpat.ProblemList.ProviderNarrativeIEN</t>
   </si>
   <si>
-    <t>Problem.ProblemExtension.ProblemDetails</t>
+    <t>Problem.Extension[ProblemExtension].ProblemDetails</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -1382,7 +1382,7 @@
     <t>Outpat.ProblemList.OnsetDateTime</t>
   </si>
   <si>
-    <t>Problem.ProblemExtension.FromTime,Problem.ProblemExtension.OnsetDate</t>
+    <t>Problem.Extension[ProblemExtension].FromTime,Problem.Extension[ProblemExtension].OnsetDate</t>
   </si>
   <si>
     <t>Condition.abatement[x]</t>
@@ -1419,7 +1419,7 @@
     <t>Outpat.ProblemList.ResolvedDateTime</t>
   </si>
   <si>
-    <t>Problem.ProblemExtension.ToTime</t>
+    <t>Problem.Extension[ProblemExtension].ToTime</t>
   </si>
   <si>
     <t>Condition.recordedDate</t>
@@ -2036,7 +2036,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="100.625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="105.5703125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="136.86328125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="68.20703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PROBLEM (9000011) to us-core-condition-problems-health-concerns</t>
+    <t>This StructureDefinition contains the maps for VistA file PROBLEM (9000011) to us-core-condition-problems-health-concerns.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -491,6 +491,9 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>2042: target not supported</t>
   </si>
   <si>
     <t>Condition.modifierExtension</t>
@@ -1012,6 +1015,10 @@
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -3312,7 +3319,7 @@
         <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>82</v>
@@ -3341,14 +3348,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3370,16 +3377,16 @@
         <v>139</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3428,7 +3435,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>83</v>
@@ -3472,10 +3479,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3498,19 +3505,19 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3559,7 +3566,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>83</v>
@@ -3583,7 +3590,7 @@
         <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3592,10 +3599,10 @@
         <v>82</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AS12" t="s" s="2">
         <v>82</v>
@@ -3603,10 +3610,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3629,13 +3636,13 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3686,7 +3693,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>83</v>
@@ -3719,7 +3726,7 @@
         <v>82</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR13" t="s" s="2">
         <v>82</v>
@@ -3730,14 +3737,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3759,13 +3766,13 @@
         <v>139</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3806,7 +3813,7 @@
         <v>142</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
@@ -3815,7 +3822,7 @@
         <v>143</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>83</v>
@@ -3848,7 +3855,7 @@
         <v>82</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>82</v>
@@ -3859,10 +3866,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3888,16 +3895,16 @@
         <v>114</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3922,13 +3929,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3946,7 +3953,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
@@ -3979,7 +3986,7 @@
         <v>137</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>82</v>
@@ -3990,10 +3997,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4016,19 +4023,19 @@
         <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4053,13 +4060,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4077,7 +4084,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -4107,10 +4114,10 @@
         <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>82</v>
@@ -4121,10 +4128,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4150,16 +4157,16 @@
         <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -4169,10 +4176,10 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -4208,7 +4215,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>83</v>
@@ -4223,7 +4230,7 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
@@ -4238,10 +4245,10 @@
         <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>82</v>
@@ -4252,10 +4259,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4278,16 +4285,16 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4301,7 +4308,7 @@
         <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>82</v>
@@ -4337,7 +4344,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>83</v>
@@ -4352,7 +4359,7 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
@@ -4367,10 +4374,10 @@
         <v>82</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>82</v>
@@ -4381,10 +4388,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4407,13 +4414,13 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4464,7 +4471,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
@@ -4494,10 +4501,10 @@
         <v>82</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>82</v>
@@ -4508,10 +4515,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4534,16 +4541,16 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4593,7 +4600,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -4623,10 +4630,10 @@
         <v>82</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>82</v>
@@ -4637,10 +4644,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4663,16 +4670,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4698,11 +4705,11 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4720,7 +4727,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
@@ -4729,34 +4736,34 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>82</v>
@@ -4764,10 +4771,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4790,16 +4797,16 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4825,11 +4832,11 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4847,7 +4854,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4856,45 +4863,45 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4917,16 +4924,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4952,19 +4959,19 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4974,7 +4981,7 @@
         <v>143</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -5001,16 +5008,16 @@
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>82</v>
@@ -5018,13 +5025,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
@@ -5046,16 +5053,16 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5066,7 +5073,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -5081,11 +5088,11 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5103,7 +5110,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5118,7 +5125,7 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
@@ -5130,16 +5137,16 @@
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>82</v>
@@ -5147,13 +5154,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>82</v>
@@ -5175,16 +5182,16 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5195,7 +5202,7 @@
         <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>82</v>
@@ -5210,13 +5217,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5234,7 +5241,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -5261,16 +5268,16 @@
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AS25" t="s" s="2">
         <v>82</v>
@@ -5278,10 +5285,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5304,16 +5311,16 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5342,10 +5349,10 @@
         <v>118</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5363,7 +5370,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -5390,31 +5397,31 @@
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5433,17 +5440,17 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5468,13 +5475,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5492,7 +5499,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -5516,30 +5523,30 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AS27" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5562,13 +5569,13 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5619,7 +5626,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5652,7 +5659,7 @@
         <v>82</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>82</v>
@@ -5663,14 +5670,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5692,13 +5699,13 @@
         <v>139</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5739,7 +5746,7 @@
         <v>142</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
@@ -5748,7 +5755,7 @@
         <v>143</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5781,7 +5788,7 @@
         <v>82</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>82</v>
@@ -5792,10 +5799,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5818,19 +5825,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5867,7 +5874,7 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>269</v>
+        <v>316</v>
       </c>
       <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
@@ -5877,7 +5884,7 @@
         <v>143</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -5907,10 +5914,10 @@
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>82</v>
@@ -5921,10 +5928,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5947,13 +5954,13 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6004,7 +6011,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6037,7 +6044,7 @@
         <v>82</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>82</v>
@@ -6048,14 +6055,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6077,13 +6084,13 @@
         <v>139</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6124,7 +6131,7 @@
         <v>142</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
@@ -6133,7 +6140,7 @@
         <v>143</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6166,7 +6173,7 @@
         <v>82</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>82</v>
@@ -6177,10 +6184,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6206,16 +6213,16 @@
         <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6225,7 +6232,7 @@
         <v>82</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>82</v>
@@ -6264,7 +6271,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6279,7 +6286,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
@@ -6294,10 +6301,10 @@
         <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>82</v>
@@ -6308,10 +6315,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6334,16 +6341,16 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6393,7 +6400,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6423,10 +6430,10 @@
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>82</v>
@@ -6437,10 +6444,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6466,14 +6473,14 @@
         <v>114</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6522,7 +6529,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6537,13 +6544,13 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
@@ -6552,10 +6559,10 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>82</v>
@@ -6566,10 +6573,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6592,17 +6599,17 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6651,7 +6658,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6681,10 +6688,10 @@
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>82</v>
@@ -6695,10 +6702,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6721,19 +6728,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6782,7 +6789,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6812,10 +6819,10 @@
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>82</v>
@@ -6826,13 +6833,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>82</v>
@@ -6854,19 +6861,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6915,7 +6922,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -6930,10 +6937,10 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>82</v>
@@ -6945,10 +6952,10 @@
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>82</v>
@@ -6959,10 +6966,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6985,13 +6992,13 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7042,7 +7049,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7075,7 +7082,7 @@
         <v>82</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>82</v>
@@ -7086,14 +7093,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7115,13 +7122,13 @@
         <v>139</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7162,7 +7169,7 @@
         <v>142</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
@@ -7171,7 +7178,7 @@
         <v>143</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7204,7 +7211,7 @@
         <v>82</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>82</v>
@@ -7215,10 +7222,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7244,16 +7251,16 @@
         <v>108</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7263,7 +7270,7 @@
         <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>82</v>
@@ -7302,7 +7309,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7317,7 +7324,7 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
@@ -7332,10 +7339,10 @@
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>82</v>
@@ -7346,10 +7353,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7372,16 +7379,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7431,7 +7438,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7461,10 +7468,10 @@
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>82</v>
@@ -7475,10 +7482,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7504,14 +7511,14 @@
         <v>114</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7560,7 +7567,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7575,10 +7582,10 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>82</v>
@@ -7590,10 +7597,10 @@
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>82</v>
@@ -7604,10 +7611,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7630,17 +7637,17 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7689,7 +7696,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7719,10 +7726,10 @@
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>82</v>
@@ -7733,10 +7740,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7759,19 +7766,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7820,7 +7827,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -7850,10 +7857,10 @@
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>82</v>
@@ -7864,10 +7871,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7890,19 +7897,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7951,7 +7958,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -7966,13 +7973,13 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7981,10 +7988,10 @@
         <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>82</v>
@@ -7995,10 +8002,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8021,16 +8028,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8056,13 +8063,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -8080,7 +8087,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8107,31 +8114,31 @@
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8150,17 +8157,17 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8209,7 +8216,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>94</v>
@@ -8224,28 +8231,28 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AS48" t="s" s="2">
         <v>82</v>
@@ -8253,10 +8260,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8279,16 +8286,16 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8338,7 +8345,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8362,19 +8369,19 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
@@ -8382,10 +8389,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8408,16 +8415,16 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8455,7 +8462,7 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8465,7 +8472,7 @@
         <v>143</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8489,19 +8496,19 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AS50" t="s" s="2">
         <v>82</v>
@@ -8509,13 +8516,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>82</v>
@@ -8537,16 +8544,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8596,7 +8603,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8611,28 +8618,28 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>82</v>
@@ -8640,10 +8647,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8666,16 +8673,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8713,7 +8720,7 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
@@ -8723,7 +8730,7 @@
         <v>143</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -8732,7 +8739,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8756,10 +8763,10 @@
         <v>82</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AS52" t="s" s="2">
         <v>82</v>
@@ -8767,13 +8774,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>82</v>
@@ -8795,16 +8802,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8854,7 +8861,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -8863,19 +8870,19 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8887,10 +8894,10 @@
         <v>82</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AS53" t="s" s="2">
         <v>82</v>
@@ -8898,10 +8905,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8924,13 +8931,13 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8981,7 +8988,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -8996,13 +9003,13 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -9011,13 +9018,13 @@
         <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AS54" t="s" s="2">
         <v>82</v>
@@ -9025,10 +9032,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9051,13 +9058,13 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9108,7 +9115,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9123,10 +9130,10 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>82</v>
@@ -9141,10 +9148,10 @@
         <v>82</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AS55" t="s" s="2">
         <v>82</v>
@@ -9152,10 +9159,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9178,13 +9185,13 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9235,7 +9242,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9265,13 +9272,13 @@
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AS56" t="s" s="2">
         <v>82</v>
@@ -9279,10 +9286,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9305,13 +9312,13 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9362,7 +9369,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9374,7 +9381,7 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9395,7 +9402,7 @@
         <v>82</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>82</v>
@@ -9406,10 +9413,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9432,13 +9439,13 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9489,7 +9496,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9522,7 +9529,7 @@
         <v>82</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>82</v>
@@ -9533,14 +9540,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9562,13 +9569,13 @@
         <v>139</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9618,7 +9625,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9651,7 +9658,7 @@
         <v>82</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>82</v>
@@ -9662,14 +9669,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9691,16 +9698,16 @@
         <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9749,7 +9756,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -9793,10 +9800,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9819,13 +9826,13 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9852,13 +9859,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9876,7 +9883,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -9885,7 +9892,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9903,13 +9910,13 @@
         <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>82</v>
@@ -9920,10 +9927,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9946,13 +9953,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10003,7 +10010,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10012,7 +10019,7 @@
         <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10036,7 +10043,7 @@
         <v>82</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>82</v>
@@ -10047,10 +10054,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10073,13 +10080,13 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10106,13 +10113,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -10130,7 +10137,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10163,7 +10170,7 @@
         <v>82</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>82</v>
@@ -10174,10 +10181,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10200,16 +10207,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10259,7 +10266,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10271,7 +10278,7 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10292,7 +10299,7 @@
         <v>82</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>82</v>
@@ -10303,10 +10310,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10329,13 +10336,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10386,7 +10393,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -10419,7 +10426,7 @@
         <v>82</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>82</v>
@@ -10430,14 +10437,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10459,13 +10466,13 @@
         <v>139</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10515,7 +10522,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10548,7 +10555,7 @@
         <v>82</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>82</v>
@@ -10559,14 +10566,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10588,16 +10595,16 @@
         <v>139</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10646,7 +10653,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -10690,10 +10697,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10716,13 +10723,13 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10749,13 +10756,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10773,7 +10780,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -10782,7 +10789,7 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>106</v>
@@ -10797,19 +10804,19 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>82</v>
@@ -10817,10 +10824,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10843,13 +10850,13 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10900,7 +10907,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -10909,7 +10916,7 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>106</v>
@@ -10933,10 +10940,10 @@
         <v>82</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AS69" t="s" s="2">
         <v>82</v>
@@ -10944,10 +10951,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10970,13 +10977,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11027,7 +11034,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11051,16 +11058,16 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -696,7 +696,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>345: source value from PROBLEM - IEN (9000011-.001)</t>
+    <t>345: source value based on PROBLEM - IEN (9000011-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -772,7 +772,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-cp-16-349:9000011-1.07: if Not Null then #resolved {null}</t>
+cp-16-349:If (9000011-1.07) is Not Null then fixed value #resolved {null}</t>
   </si>
   <si>
     <t>605: terminologyMaps using VF_problemStatus on PROBLEM - STATUS (9000011-.12)</t>
@@ -1102,7 +1102,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>366: source value from PROBLEM - SNOMED CT CONCEPT CODE (9000011-80001)</t>
+    <t>366: source value based on PROBLEM - SNOMED CT CONCEPT CODE (9000011-80001)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.SNOMEDCTConceptCode</t>
@@ -1172,7 +1172,7 @@
     <t>va-icd</t>
   </si>
   <si>
-    <t>365: source value from PROBLEM - DIAGNOSIS &gt; ICD DIAGNOSIS (9000011-.01 &gt; 80-)</t>
+    <t>365: source value based on PROBLEM - DIAGNOSIS &gt; ICD DIAGNOSIS (9000011-.01 &gt; 80-)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.ICDIEN</t>
@@ -1199,7 +1199,7 @@
     <t>Condition.code.coding:va-icd.code</t>
   </si>
   <si>
-    <t>365-2: source value from PROBLEM - DIAGNOSIS &gt; ICD DIAGNOSIS - CODE NUMBER (9000011-.01 &gt; 80-.01)</t>
+    <t>365-2: source value based on PROBLEM - DIAGNOSIS &gt; ICD DIAGNOSIS - CODE NUMBER (9000011-.01 &gt; 80-.01)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.ICDIEN
@@ -1230,7 +1230,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>957: source value from PROBLEM - PROVIDER NARRATIVE (9000011-.05)</t>
+    <t>957: source value based on PROBLEM - PROVIDER NARRATIVE (9000011-.05)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.ProviderNarrativeIEN</t>
@@ -1295,7 +1295,7 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
-    <t>367: reference from PROBLEM - PATIENT NAME (9000011-.02)</t>
+    <t>367: reference based on PROBLEM - PATIENT NAME (9000011-.02)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.PatientIEN</t>
@@ -1383,7 +1383,7 @@
 </t>
   </si>
   <si>
-    <t>369: source value from PROBLEM - DATE OF ONSET (9000011-.13)</t>
+    <t>369: source value based on PROBLEM - DATE OF ONSET (9000011-.13)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.OnsetDateTime</t>
@@ -1420,7 +1420,7 @@
     <t>abatementDateTime</t>
   </si>
   <si>
-    <t>1761: source value from PROBLEM - DATE RESOLVED (9000011-1.07)</t>
+    <t>1761: source value based on PROBLEM - DATE RESOLVED (9000011-1.07)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.ResolvedDateTime</t>
@@ -1438,7 +1438,7 @@
     <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
   </si>
   <si>
-    <t>371: source value from PROBLEM - DATE ENTERED (9000011-.08)</t>
+    <t>371: source value based on PROBLEM - DATE ENTERED (9000011-.08)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.EnteredDateTime</t>
@@ -1469,7 +1469,7 @@
     <t>Individual who recorded the record and takes responsibility for its content.</t>
   </si>
   <si>
-    <t>373: source value from PROBLEM - RECORDING PROVIDER (9000011-1.04)</t>
+    <t>373: source value based on PROBLEM - RECORDING PROVIDER (9000011-1.04)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.RecordingProviderIEN</t>
@@ -2041,7 +2041,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="100.625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="104.71875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="136.86328125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2906" uniqueCount="535">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -764,6 +764,9 @@
     <t>The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
+    <t>see mapping [VF_problemStatus](ConceptMap-VF-problemStatus.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/problemStatus</t>
   </si>
   <si>
@@ -811,6 +814,9 @@
   <si>
     <t>verificationStatus is not required.  For example, when a patient has abdominal pain in the ED, there is not likely going to be a verification status.
 The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_problemVerificationStatus](ConceptMap-VF-problemVerificationStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/problemVerificationStatus</t>
@@ -4707,9 +4713,11 @@
       <c r="X21" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y21" s="2"/>
+      <c r="Y21" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4736,34 +4744,34 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>82</v>
@@ -4771,10 +4779,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4800,13 +4808,13 @@
         <v>192</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4834,9 +4842,11 @@
       <c r="X22" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y22" s="2"/>
+      <c r="Y22" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4854,7 +4864,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4863,45 +4873,45 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4927,13 +4937,13 @@
         <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4962,16 +4972,16 @@
         <v>197</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4981,7 +4991,7 @@
         <v>143</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -5008,16 +5018,16 @@
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>82</v>
@@ -5025,13 +5035,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
@@ -5056,13 +5066,13 @@
         <v>192</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5073,7 +5083,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -5092,7 +5102,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5110,7 +5120,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5125,7 +5135,7 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
@@ -5137,16 +5147,16 @@
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>82</v>
@@ -5154,13 +5164,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>82</v>
@@ -5185,13 +5195,13 @@
         <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5202,7 +5212,7 @@
         <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>82</v>
@@ -5220,28 +5230,28 @@
         <v>197</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -5268,16 +5278,16 @@
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AS25" t="s" s="2">
         <v>82</v>
@@ -5285,10 +5295,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5314,13 +5324,13 @@
         <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5349,28 +5359,28 @@
         <v>118</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -5397,31 +5407,31 @@
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5443,14 +5453,14 @@
         <v>192</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5478,10 +5488,10 @@
         <v>197</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5499,7 +5509,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -5523,30 +5533,30 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AS27" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5670,10 +5680,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5799,10 +5809,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5825,19 +5835,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5874,7 +5884,7 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
@@ -5884,7 +5894,7 @@
         <v>143</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -5914,10 +5924,10 @@
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>82</v>
@@ -5928,10 +5938,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6055,10 +6065,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6184,10 +6194,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6213,16 +6223,16 @@
         <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6232,7 +6242,7 @@
         <v>82</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>82</v>
@@ -6271,7 +6281,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6286,7 +6296,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
@@ -6301,10 +6311,10 @@
         <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>82</v>
@@ -6315,10 +6325,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6344,13 +6354,13 @@
         <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6400,7 +6410,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6430,10 +6440,10 @@
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>82</v>
@@ -6444,10 +6454,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6473,14 +6483,14 @@
         <v>114</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6529,7 +6539,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6544,13 +6554,13 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
@@ -6559,10 +6569,10 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>82</v>
@@ -6573,10 +6583,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6602,14 +6612,14 @@
         <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6658,7 +6668,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6688,10 +6698,10 @@
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>82</v>
@@ -6702,10 +6712,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6728,19 +6738,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6789,7 +6799,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6819,10 +6829,10 @@
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>82</v>
@@ -6833,13 +6843,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>82</v>
@@ -6861,19 +6871,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6922,7 +6932,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -6937,10 +6947,10 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>82</v>
@@ -6952,10 +6962,10 @@
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>82</v>
@@ -6966,10 +6976,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7093,10 +7103,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7222,10 +7232,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7251,16 +7261,16 @@
         <v>108</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7270,7 +7280,7 @@
         <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>82</v>
@@ -7309,7 +7319,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7324,7 +7334,7 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
@@ -7339,10 +7349,10 @@
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>82</v>
@@ -7353,10 +7363,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7382,13 +7392,13 @@
         <v>171</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7438,7 +7448,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7468,10 +7478,10 @@
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>82</v>
@@ -7482,10 +7492,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7511,14 +7521,14 @@
         <v>114</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7567,7 +7577,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7582,10 +7592,10 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>82</v>
@@ -7597,10 +7607,10 @@
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>82</v>
@@ -7611,10 +7621,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7640,14 +7650,14 @@
         <v>171</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7696,7 +7706,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7726,10 +7736,10 @@
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>82</v>
@@ -7740,10 +7750,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7766,19 +7776,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7827,7 +7837,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -7857,10 +7867,10 @@
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>82</v>
@@ -7871,10 +7881,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7900,16 +7910,16 @@
         <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7958,7 +7968,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -7973,13 +7983,13 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7988,10 +7998,10 @@
         <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>82</v>
@@ -8002,10 +8012,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8031,13 +8041,13 @@
         <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8063,13 +8073,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -8087,7 +8097,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8114,31 +8124,31 @@
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8157,17 +8167,17 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8216,7 +8226,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>94</v>
@@ -8231,28 +8241,28 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AS48" t="s" s="2">
         <v>82</v>
@@ -8260,10 +8270,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8286,16 +8296,16 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8345,7 +8355,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8369,19 +8379,19 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
@@ -8389,10 +8399,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8415,16 +8425,16 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8462,7 +8472,7 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8472,7 +8482,7 @@
         <v>143</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8496,19 +8506,19 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AS50" t="s" s="2">
         <v>82</v>
@@ -8516,13 +8526,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>82</v>
@@ -8544,16 +8554,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8603,7 +8613,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8618,28 +8628,28 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>82</v>
@@ -8647,10 +8657,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8673,16 +8683,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8720,7 +8730,7 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
@@ -8730,7 +8740,7 @@
         <v>143</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -8739,7 +8749,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8763,10 +8773,10 @@
         <v>82</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AS52" t="s" s="2">
         <v>82</v>
@@ -8774,13 +8784,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>82</v>
@@ -8802,16 +8812,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8861,7 +8871,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -8870,19 +8880,19 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8894,10 +8904,10 @@
         <v>82</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AS53" t="s" s="2">
         <v>82</v>
@@ -8905,10 +8915,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8931,13 +8941,13 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8988,7 +8998,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9003,13 +9013,13 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -9018,13 +9028,13 @@
         <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AS54" t="s" s="2">
         <v>82</v>
@@ -9032,10 +9042,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9058,13 +9068,13 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9115,7 +9125,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9130,10 +9140,10 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>82</v>
@@ -9148,10 +9158,10 @@
         <v>82</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AS55" t="s" s="2">
         <v>82</v>
@@ -9159,10 +9169,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9185,13 +9195,13 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9242,7 +9252,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9272,13 +9282,13 @@
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AS56" t="s" s="2">
         <v>82</v>
@@ -9286,10 +9296,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9312,13 +9322,13 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9369,7 +9379,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9381,7 +9391,7 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9402,7 +9412,7 @@
         <v>82</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>82</v>
@@ -9413,10 +9423,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9540,10 +9550,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9669,14 +9679,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9698,10 +9708,10 @@
         <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>158</v>
@@ -9756,7 +9766,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -9800,10 +9810,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9829,10 +9839,10 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9859,13 +9869,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9883,7 +9893,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -9892,7 +9902,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9910,13 +9920,13 @@
         <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>82</v>
@@ -9927,10 +9937,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9953,13 +9963,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10010,7 +10020,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10019,7 +10029,7 @@
         <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10043,7 +10053,7 @@
         <v>82</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>82</v>
@@ -10054,10 +10064,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10083,10 +10093,10 @@
         <v>192</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10113,13 +10123,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -10137,7 +10147,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10170,7 +10180,7 @@
         <v>82</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>82</v>
@@ -10181,10 +10191,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10207,16 +10217,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10266,7 +10276,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10278,7 +10288,7 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10299,7 +10309,7 @@
         <v>82</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>82</v>
@@ -10310,10 +10320,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10437,10 +10447,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10566,14 +10576,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10595,10 +10605,10 @@
         <v>139</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>158</v>
@@ -10653,7 +10663,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -10697,10 +10707,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10726,10 +10736,10 @@
         <v>192</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10756,13 +10766,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10780,7 +10790,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -10789,7 +10799,7 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>106</v>
@@ -10804,19 +10814,19 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>82</v>
@@ -10824,10 +10834,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10850,13 +10860,13 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10907,7 +10917,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -10916,7 +10926,7 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>106</v>
@@ -10940,10 +10950,10 @@
         <v>82</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AS69" t="s" s="2">
         <v>82</v>
@@ -10951,10 +10961,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10977,13 +10987,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11034,7 +11044,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11058,16 +11068,16 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -775,7 +775,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-cp-16-349:If (9000011-1.07) is Not Null then fixed value #resolved {null}</t>
+cp-16-349:If (9000011-1.07) is Not Null then fixed value #resolved {true}</t>
   </si>
   <si>
     <t>605: terminologyMaps using VF_problemStatus on PROBLEM - STATUS (9000011-.12)</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2906" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="552">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -493,6 +493,80 @@
 </t>
   </si>
   <si>
+    <t>Condition.extension:assertedDate.id</t>
+  </si>
+  <si>
+    <t>Condition.extension.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Condition.extension:assertedDate.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension:assertedDate.url</t>
+  </si>
+  <si>
+    <t>Condition.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/condition-assertedDate</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Condition.extension:assertedDate.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
     <t>2042: target not supported</t>
   </si>
   <si>
@@ -554,18 +628,6 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Condition.identifier.extension</t>
   </si>
   <si>
@@ -573,12 +635,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Condition.identifier.use</t>
@@ -1383,10 +1439,6 @@
   </si>
   <si>
     <t>onsetDateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
   </si>
   <si>
     <t>369: source value based on PROBLEM - DATE OF ONSET (9000011-.13)</t>
@@ -2009,7 +2061,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS70"/>
+  <dimension ref="A1:AS74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.5390625" customWidth="true" bestFit="true"/>
@@ -3325,7 +3377,7 @@
         <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>82</v>
@@ -3354,46 +3406,42 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>154</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M11" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>159</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3441,19 +3489,19 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
@@ -3474,7 +3522,7 @@
         <v>82</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>82</v>
@@ -3485,10 +3533,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3499,7 +3547,7 @@
         <v>83</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -3508,23 +3556,19 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3560,19 +3604,19 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>83</v>
@@ -3584,7 +3628,7 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>82</v>
@@ -3596,7 +3640,7 @@
         <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3605,10 +3649,10 @@
         <v>82</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AR12" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AS12" t="s" s="2">
         <v>82</v>
@@ -3616,10 +3660,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3627,7 +3671,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>94</v>
@@ -3642,22 +3686,24 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>82</v>
@@ -3699,10 +3745,10 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>94</v>
@@ -3732,7 +3778,7 @@
         <v>82</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="AR13" t="s" s="2">
         <v>82</v>
@@ -3743,21 +3789,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
@@ -3769,17 +3815,15 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3816,34 +3860,34 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>82</v>
@@ -3861,7 +3905,7 @@
         <v>82</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>82</v>
@@ -3872,21 +3916,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
@@ -3895,22 +3939,22 @@
         <v>95</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3935,13 +3979,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3959,19 +4003,19 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3989,10 +4033,10 @@
         <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ15" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>82</v>
@@ -4003,10 +4047,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4017,7 +4061,7 @@
         <v>83</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -4029,19 +4073,19 @@
         <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4066,13 +4110,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4090,13 +4134,13 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -4114,19 +4158,19 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>82</v>
+        <v>191</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="AS16" t="s" s="2">
         <v>82</v>
@@ -4134,10 +4178,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4151,29 +4195,25 @@
         <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>108</v>
+        <v>195</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
@@ -4182,10 +4222,10 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -4221,7 +4261,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>157</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>83</v>
@@ -4233,10 +4273,10 @@
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
@@ -4251,10 +4291,10 @@
         <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>82</v>
@@ -4265,42 +4305,42 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4314,7 +4354,7 @@
         <v>82</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>82</v>
@@ -4338,34 +4378,34 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
@@ -4380,10 +4420,10 @@
         <v>82</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>220</v>
+        <v>82</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>221</v>
+        <v>158</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>82</v>
@@ -4394,10 +4434,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4414,22 +4454,26 @@
         <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>223</v>
+        <v>114</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4453,13 +4497,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -4477,7 +4521,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
@@ -4507,10 +4551,10 @@
         <v>82</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>82</v>
@@ -4521,10 +4565,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4547,18 +4591,20 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4582,13 +4628,13 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4606,7 +4652,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -4636,10 +4682,10 @@
         <v>82</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>82</v>
@@ -4650,10 +4696,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4670,24 +4716,26 @@
         <v>95</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4696,10 +4744,10 @@
         <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>82</v>
@@ -4711,13 +4759,13 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4735,7 +4783,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
@@ -4744,34 +4792,34 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>82</v>
@@ -4779,10 +4827,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4799,22 +4847,22 @@
         <v>95</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4828,7 +4876,7 @@
         <v>82</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>82</v>
@@ -4840,13 +4888,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>257</v>
+        <v>82</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4864,7 +4912,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4873,45 +4921,45 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4919,32 +4967,30 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G23" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4969,35 +5015,37 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
@@ -5018,16 +5066,16 @@
         <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>82</v>
@@ -5035,44 +5083,42 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G24" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="H24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>192</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5083,7 +5129,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -5098,11 +5144,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5120,13 +5168,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -5135,7 +5183,7 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
@@ -5147,16 +5195,16 @@
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>82</v>
@@ -5164,14 +5212,12 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5186,22 +5232,22 @@
         <v>95</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5212,7 +5258,7 @@
         <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>82</v>
@@ -5227,67 +5273,67 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AR25" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AS25" t="s" s="2">
         <v>82</v>
@@ -5295,10 +5341,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5312,25 +5358,25 @@
         <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5356,13 +5402,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5380,7 +5426,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -5389,56 +5435,56 @@
         <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>94</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>95</v>
@@ -5447,21 +5493,21 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5485,37 +5531,35 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5533,44 +5577,46 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="AS27" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
@@ -5579,15 +5625,17 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>172</v>
+        <v>297</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5597,7 +5645,7 @@
         <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>82</v>
@@ -5612,13 +5660,11 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5636,22 +5682,22 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>174</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
@@ -5663,16 +5709,16 @@
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AS28" t="s" s="2">
         <v>82</v>
@@ -5680,24 +5726,26 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="D29" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
@@ -5706,16 +5754,16 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>177</v>
+        <v>303</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>178</v>
+        <v>287</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>158</v>
+        <v>288</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5726,7 +5774,7 @@
         <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>82</v>
@@ -5741,31 +5789,31 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5777,7 +5825,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5792,16 +5840,16 @@
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AS29" t="s" s="2">
         <v>82</v>
@@ -5809,10 +5857,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5823,7 +5871,7 @@
         <v>83</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5832,23 +5880,21 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>313</v>
+        <v>210</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5872,35 +5918,37 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AC30" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5921,59 +5969,61 @@
         <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="AS30" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>172</v>
+        <v>317</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>173</v>
+        <v>318</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5997,13 +6047,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -6021,7 +6071,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>174</v>
+        <v>315</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6033,7 +6083,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6045,41 +6095,41 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AS31" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6091,17 +6141,15 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6138,31 +6186,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6183,7 +6231,7 @@
         <v>82</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>82</v>
@@ -6194,46 +6242,44 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>325</v>
+        <v>197</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>326</v>
+        <v>198</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6242,7 +6288,7 @@
         <v>82</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>82</v>
@@ -6269,34 +6315,34 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>330</v>
+        <v>162</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
@@ -6311,10 +6357,10 @@
         <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>333</v>
+        <v>158</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>82</v>
@@ -6325,10 +6371,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6339,7 +6385,7 @@
         <v>83</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6351,18 +6397,20 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>171</v>
+        <v>331</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6398,25 +6446,23 @@
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -6440,10 +6486,10 @@
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>82</v>
@@ -6454,10 +6500,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6471,27 +6517,25 @@
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>342</v>
+        <v>155</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>343</v>
+        <v>156</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>344</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6539,7 +6583,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>345</v>
+        <v>157</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6551,16 +6595,16 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
@@ -6569,10 +6613,10 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>350</v>
+        <v>158</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>82</v>
@@ -6583,21 +6627,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6606,21 +6650,21 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>352</v>
+        <v>197</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6656,31 +6700,31 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>355</v>
+        <v>162</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6698,10 +6742,10 @@
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>357</v>
+        <v>158</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>82</v>
@@ -6712,10 +6756,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6729,7 +6773,7 @@
         <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6738,19 +6782,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>359</v>
+        <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6760,7 +6804,7 @@
         <v>82</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>82</v>
@@ -6799,7 +6843,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6814,7 +6858,7 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
@@ -6829,10 +6873,10 @@
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>82</v>
@@ -6843,14 +6887,12 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6862,7 +6904,7 @@
         <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6871,20 +6913,18 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>313</v>
+        <v>195</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>315</v>
+        <v>354</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6932,13 +6972,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6947,10 +6987,10 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>82</v>
@@ -6962,10 +7002,10 @@
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>82</v>
@@ -6976,10 +7016,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>359</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6993,25 +7033,27 @@
         <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>172</v>
+        <v>360</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>173</v>
+        <v>361</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -7059,7 +7101,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>174</v>
+        <v>363</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7071,16 +7113,16 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -7089,10 +7131,10 @@
         <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>175</v>
+        <v>368</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>82</v>
@@ -7103,21 +7145,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>369</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7126,21 +7168,21 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>177</v>
+        <v>370</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7176,31 +7218,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>180</v>
+        <v>373</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7218,10 +7260,10 @@
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>175</v>
+        <v>375</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>82</v>
@@ -7232,10 +7274,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>324</v>
+        <v>376</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7249,7 +7291,7 @@
         <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
@@ -7258,19 +7300,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>108</v>
+        <v>377</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>325</v>
+        <v>378</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>326</v>
+        <v>379</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7280,7 +7322,7 @@
         <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>82</v>
@@ -7319,7 +7361,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7334,7 +7376,7 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
@@ -7349,10 +7391,10 @@
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>332</v>
+        <v>383</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>333</v>
+        <v>384</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>82</v>
@@ -7363,12 +7405,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7380,7 +7424,7 @@
         <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7389,18 +7433,20 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>171</v>
+        <v>331</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O42" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7448,13 +7494,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7463,10 +7509,10 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>82</v>
@@ -7478,10 +7524,10 @@
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>82</v>
@@ -7492,10 +7538,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7509,27 +7555,25 @@
         <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>342</v>
+        <v>155</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>343</v>
+        <v>156</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>344</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7577,7 +7621,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>345</v>
+        <v>157</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7589,13 +7633,13 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>379</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>82</v>
@@ -7607,10 +7651,10 @@
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>350</v>
+        <v>158</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>82</v>
@@ -7621,21 +7665,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7644,21 +7688,21 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>352</v>
+        <v>197</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7694,31 +7738,31 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>355</v>
+        <v>162</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7736,10 +7780,10 @@
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>357</v>
+        <v>158</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>82</v>
@@ -7750,10 +7794,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7767,7 +7811,7 @@
         <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7776,19 +7820,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>359</v>
+        <v>108</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7798,7 +7842,7 @@
         <v>82</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>82</v>
@@ -7837,7 +7881,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -7852,7 +7896,7 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
@@ -7867,10 +7911,10 @@
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>82</v>
@@ -7881,10 +7925,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7898,7 +7942,7 @@
         <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>82</v>
@@ -7907,20 +7951,18 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7968,7 +8010,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -7983,13 +8025,13 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7998,10 +8040,10 @@
         <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>82</v>
@@ -8012,10 +8054,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8026,10 +8068,10 @@
         <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
@@ -8038,18 +8080,18 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>394</v>
+        <v>360</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8073,13 +8115,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -8097,13 +8139,13 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
@@ -8112,10 +8154,10 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>82</v>
@@ -8124,41 +8166,41 @@
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
@@ -8167,17 +8209,17 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>405</v>
+        <v>195</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>406</v>
+        <v>370</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>407</v>
+        <v>371</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>408</v>
+        <v>372</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8226,10 +8268,10 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>94</v>
@@ -8241,28 +8283,28 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>412</v>
+        <v>374</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>413</v>
+        <v>375</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="AS48" t="s" s="2">
         <v>82</v>
@@ -8270,10 +8312,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>415</v>
+        <v>376</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8296,18 +8338,20 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>416</v>
+        <v>377</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>417</v>
+        <v>378</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>418</v>
+        <v>379</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8355,7 +8399,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8379,19 +8423,19 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>421</v>
+        <v>383</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>422</v>
+        <v>384</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
@@ -8399,10 +8443,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8425,18 +8469,20 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>425</v>
+        <v>195</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8472,17 +8518,19 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8497,28 +8545,28 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>432</v>
+        <v>410</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AS50" t="s" s="2">
         <v>82</v>
@@ -8526,14 +8574,12 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8542,10 +8588,10 @@
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
@@ -8554,16 +8600,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>436</v>
+        <v>210</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8589,13 +8635,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8613,13 +8659,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8628,47 +8674,47 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>94</v>
@@ -8680,21 +8726,21 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L52" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8730,53 +8776,55 @@
         <v>82</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AC52" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="AS52" t="s" s="2">
         <v>82</v>
@@ -8784,14 +8832,12 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8803,25 +8849,25 @@
         <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K53" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>442</v>
-      </c>
       <c r="N53" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8871,7 +8917,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -8880,34 +8926,34 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AS53" t="s" s="2">
         <v>82</v>
@@ -8915,10 +8961,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8941,15 +8987,17 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8986,19 +9034,17 @@
         <v>82</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9013,28 +9059,28 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="AS54" t="s" s="2">
         <v>82</v>
@@ -9042,12 +9088,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9068,15 +9116,17 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>462</v>
+        <v>172</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9125,7 +9175,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9140,28 +9190,28 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="AS55" t="s" s="2">
         <v>82</v>
@@ -9169,10 +9219,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9186,24 +9236,26 @@
         <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9240,19 +9292,17 @@
         <v>82</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9261,7 +9311,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9282,13 +9332,13 @@
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="AS56" t="s" s="2">
         <v>82</v>
@@ -9296,12 +9346,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9310,10 +9362,10 @@
         <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
@@ -9322,15 +9374,17 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>476</v>
+        <v>172</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9379,28 +9433,28 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>479</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9412,10 +9466,10 @@
         <v>82</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
       <c r="AS57" t="s" s="2">
         <v>82</v>
@@ -9423,10 +9477,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9440,22 +9494,22 @@
         <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>172</v>
+        <v>470</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>173</v>
+        <v>471</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9506,7 +9560,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>174</v>
+        <v>469</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9518,16 +9572,16 @@
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9536,13 +9590,13 @@
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>175</v>
+        <v>476</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AS58" t="s" s="2">
         <v>82</v>
@@ -9550,43 +9604,41 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>139</v>
+        <v>479</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>177</v>
+        <v>480</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9635,25 +9687,25 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>180</v>
+        <v>478</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>82</v>
@@ -9668,10 +9720,10 @@
         <v>82</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>175</v>
+        <v>484</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="AS59" t="s" s="2">
         <v>82</v>
@@ -9679,46 +9731,42 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>139</v>
+        <v>479</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9766,19 +9814,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9796,13 +9844,13 @@
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>82</v>
+        <v>489</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>137</v>
+        <v>490</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AS60" t="s" s="2">
         <v>82</v>
@@ -9810,10 +9858,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9824,7 +9872,7 @@
         <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9836,13 +9884,13 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>192</v>
+        <v>493</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9869,43 +9917,43 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AA61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>106</v>
+        <v>496</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9920,13 +9968,13 @@
         <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>307</v>
+        <v>497</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>82</v>
@@ -9937,10 +9985,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9951,7 +9999,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9963,13 +10011,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>496</v>
+        <v>195</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>497</v>
+        <v>155</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>498</v>
+        <v>156</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10020,19 +10068,19 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>495</v>
+        <v>157</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -10053,7 +10101,7 @@
         <v>82</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>499</v>
+        <v>158</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>82</v>
@@ -10064,21 +10112,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -10090,15 +10138,17 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>501</v>
+        <v>197</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10123,13 +10173,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -10147,19 +10197,19 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>500</v>
+        <v>162</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10180,7 +10230,7 @@
         <v>82</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>505</v>
+        <v>158</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>82</v>
@@ -10191,14 +10241,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10211,24 +10261,26 @@
         <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>476</v>
+        <v>139</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10276,7 +10328,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10288,7 +10340,7 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>510</v>
+        <v>145</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10309,7 +10361,7 @@
         <v>82</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>511</v>
+        <v>137</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>82</v>
@@ -10320,10 +10372,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10346,13 +10398,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>172</v>
+        <v>506</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>173</v>
+        <v>507</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10379,13 +10431,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>82</v>
+        <v>508</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10403,7 +10455,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>174</v>
+        <v>505</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -10412,10 +10464,10 @@
         <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10430,13 +10482,13 @@
         <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>82</v>
@@ -10447,14 +10499,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10473,17 +10525,15 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>139</v>
+        <v>513</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>177</v>
+        <v>514</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10532,7 +10582,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>180</v>
+        <v>512</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10541,10 +10591,10 @@
         <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10565,7 +10615,7 @@
         <v>82</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>175</v>
+        <v>516</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>82</v>
@@ -10576,46 +10626,42 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>485</v>
+        <v>518</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10639,13 +10685,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10663,19 +10709,19 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10696,7 +10742,7 @@
         <v>82</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>137</v>
+        <v>522</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>82</v>
@@ -10707,10 +10753,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10730,18 +10776,20 @@
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>192</v>
+        <v>493</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10766,13 +10814,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10790,7 +10838,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -10799,10 +10847,10 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>106</v>
+        <v>527</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10814,19 +10862,19 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>82</v>
@@ -10834,10 +10882,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10848,7 +10896,7 @@
         <v>83</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10857,16 +10905,16 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>525</v>
+        <v>195</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>526</v>
+        <v>155</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>527</v>
+        <v>156</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10917,19 +10965,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>524</v>
+        <v>157</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10950,10 +10998,10 @@
         <v>82</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>499</v>
+        <v>158</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
       <c r="AS69" t="s" s="2">
         <v>82</v>
@@ -10961,14 +11009,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10987,15 +11035,17 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>529</v>
+        <v>139</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>530</v>
+        <v>197</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -11044,7 +11094,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>528</v>
+        <v>162</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11056,38 +11106,550 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AR70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS70" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS71" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS70" t="s" s="2">
+      <c r="AK72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AR72" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AS72" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AR73" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AS73" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AR74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS74" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS70">
+  <autoFilter ref="A1:AS74">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11097,7 +11659,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1357,7 +1357,7 @@
     <t>Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
-    <t>367: reference based on PROBLEM - PATIENT NAME (9000011-.02)</t>
+    <t>367: reference based on PROBLEM - PATIENT NAME &gt; PATIENT/IHS - NAME (9000011-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Outpat.ProblemList.PatientIEN</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ConditionProblem.xlsx
+++ b/docs/StructureDefinition-ConditionProblem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
